--- a/research/traditional_assets/database/data/argentina/argentina_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_paper_forest_products.xlsx
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1812003182214515</v>
+        <v>0.1805953671076764</v>
       </c>
       <c r="C2">
-        <v>260.2272515485877</v>
+        <v>258.9851127449776</v>
       </c>
       <c r="D2">
-        <v>252.6472515485877</v>
+        <v>253.7811127449776</v>
       </c>
       <c r="E2">
-        <v>-146.3</v>
+        <v>-143.924</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.376</v>
       </c>
       <c r="G2">
         <v>7.58</v>
@@ -1567,28 +1567,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1195128</v>
       </c>
       <c r="N2">
-        <v>59.76666666666667</v>
+        <v>59.64715386666666</v>
       </c>
       <c r="O2">
-        <v>20.91833333333333</v>
+        <v>20.87650385333333</v>
       </c>
       <c r="P2">
-        <v>38.84833333333333</v>
+        <v>38.77065001333333</v>
       </c>
       <c r="Q2">
-        <v>64.24833333333333</v>
+        <v>64.17065001333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1812003182214515</v>
+        <v>0.1820893102097741</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6696401059209474</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>500.0859043271236</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1805953671076764</v>
+        <v>0.1799904159939013</v>
       </c>
       <c r="C3">
-        <v>258.9851127449776</v>
+        <v>257.7531971840416</v>
       </c>
       <c r="D3">
-        <v>253.7811127449776</v>
+        <v>254.9251971840416</v>
       </c>
       <c r="E3">
-        <v>-143.924</v>
+        <v>-141.548</v>
       </c>
       <c r="F3">
-        <v>2.376</v>
+        <v>4.752000000000001</v>
       </c>
       <c r="G3">
         <v>7.58</v>
@@ -1649,28 +1649,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M3">
-        <v>0.1195128</v>
+        <v>0.2390256</v>
       </c>
       <c r="N3">
-        <v>59.64715386666666</v>
+        <v>59.52764106666667</v>
       </c>
       <c r="O3">
-        <v>20.87650385333333</v>
+        <v>20.83467437333333</v>
       </c>
       <c r="P3">
-        <v>38.77065001333333</v>
+        <v>38.69296669333333</v>
       </c>
       <c r="Q3">
-        <v>64.17065001333333</v>
+        <v>64.09296669333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1820893102097741</v>
+        <v>0.182996444891736</v>
       </c>
       <c r="T3">
-        <v>0.6696401059209474</v>
+        <v>0.6740971962355036</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>500.0859043271236</v>
+        <v>250.0429521635618</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1799904159939013</v>
+        <v>0.1793854648801262</v>
       </c>
       <c r="C4">
-        <v>257.7531971840416</v>
+        <v>256.5316437557867</v>
       </c>
       <c r="D4">
-        <v>254.9251971840416</v>
+        <v>256.0796437557867</v>
       </c>
       <c r="E4">
-        <v>-141.548</v>
+        <v>-139.172</v>
       </c>
       <c r="F4">
-        <v>4.752000000000001</v>
+        <v>7.128</v>
       </c>
       <c r="G4">
         <v>7.58</v>
@@ -1731,28 +1731,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M4">
-        <v>0.2390256</v>
+        <v>0.3585384</v>
       </c>
       <c r="N4">
-        <v>59.52764106666667</v>
+        <v>59.40812826666667</v>
       </c>
       <c r="O4">
-        <v>20.83467437333333</v>
+        <v>20.79284489333333</v>
       </c>
       <c r="P4">
-        <v>38.69296669333333</v>
+        <v>38.61528337333333</v>
       </c>
       <c r="Q4">
-        <v>64.09296669333334</v>
+        <v>64.01528337333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.182996444891736</v>
+        <v>0.1839222833815734</v>
       </c>
       <c r="T4">
-        <v>0.6740971962355036</v>
+        <v>0.678646185319432</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>250.0429521635618</v>
+        <v>166.6953014423746</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1793854648801262</v>
+        <v>0.1787805137663511</v>
       </c>
       <c r="C5">
-        <v>256.5316437557867</v>
+        <v>255.3205938775569</v>
       </c>
       <c r="D5">
-        <v>256.0796437557867</v>
+        <v>257.244593877557</v>
       </c>
       <c r="E5">
-        <v>-139.172</v>
+        <v>-136.796</v>
       </c>
       <c r="F5">
-        <v>7.128</v>
+        <v>9.504000000000001</v>
       </c>
       <c r="G5">
         <v>7.58</v>
@@ -1813,28 +1813,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M5">
-        <v>0.3585384</v>
+        <v>0.4780512000000001</v>
       </c>
       <c r="N5">
-        <v>59.40812826666667</v>
+        <v>59.28861546666666</v>
       </c>
       <c r="O5">
-        <v>20.79284489333333</v>
+        <v>20.75101541333333</v>
       </c>
       <c r="P5">
-        <v>38.61528337333333</v>
+        <v>38.53760005333334</v>
       </c>
       <c r="Q5">
-        <v>64.01528337333333</v>
+        <v>63.93760005333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1839222833815734</v>
+        <v>0.1848674101732824</v>
       </c>
       <c r="T5">
-        <v>0.678646185319432</v>
+        <v>0.6832899450092756</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>166.6953014423746</v>
+        <v>125.0214760817809</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1787805137663511</v>
+        <v>0.1781755626525761</v>
       </c>
       <c r="C6">
-        <v>255.3205938775569</v>
+        <v>254.1201915517838</v>
       </c>
       <c r="D6">
-        <v>257.244593877557</v>
+        <v>258.4201915517838</v>
       </c>
       <c r="E6">
-        <v>-136.796</v>
+        <v>-134.42</v>
       </c>
       <c r="F6">
-        <v>9.504000000000001</v>
+        <v>11.88</v>
       </c>
       <c r="G6">
         <v>7.58</v>
@@ -1895,28 +1895,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M6">
-        <v>0.4780512000000001</v>
+        <v>0.5975640000000001</v>
       </c>
       <c r="N6">
-        <v>59.28861546666666</v>
+        <v>59.16910266666667</v>
       </c>
       <c r="O6">
-        <v>20.75101541333333</v>
+        <v>20.70918593333333</v>
       </c>
       <c r="P6">
-        <v>38.53760005333334</v>
+        <v>38.45991673333333</v>
       </c>
       <c r="Q6">
-        <v>63.93760005333334</v>
+        <v>63.85991673333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1848674101732824</v>
+        <v>0.1858324343711327</v>
       </c>
       <c r="T6">
-        <v>0.6832899450092756</v>
+        <v>0.6880314680610108</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>125.0214760817809</v>
+        <v>100.0171808654247</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1781755626525761</v>
+        <v>0.177570611538801</v>
       </c>
       <c r="C7">
-        <v>254.1201915517838</v>
+        <v>252.9305834253252</v>
       </c>
       <c r="D7">
-        <v>258.4201915517838</v>
+        <v>259.6065834253253</v>
       </c>
       <c r="E7">
-        <v>-134.42</v>
+        <v>-132.044</v>
       </c>
       <c r="F7">
-        <v>11.88</v>
+        <v>14.256</v>
       </c>
       <c r="G7">
         <v>7.58</v>
@@ -1977,28 +1977,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M7">
-        <v>0.5975640000000001</v>
+        <v>0.7170768000000001</v>
       </c>
       <c r="N7">
-        <v>59.16910266666667</v>
+        <v>59.04958986666666</v>
       </c>
       <c r="O7">
-        <v>20.70918593333333</v>
+        <v>20.66735645333333</v>
       </c>
       <c r="P7">
-        <v>38.45991673333333</v>
+        <v>38.38223341333334</v>
       </c>
       <c r="Q7">
-        <v>63.85991673333334</v>
+        <v>63.78223341333334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1858324343711327</v>
+        <v>0.1868179909987245</v>
       </c>
       <c r="T7">
-        <v>0.6880314680610108</v>
+        <v>0.6928738745819318</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>100.0171808654247</v>
+        <v>83.34765072118726</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.177570611538801</v>
+        <v>0.1769656604250259</v>
       </c>
       <c r="C8">
-        <v>252.9305834253252</v>
+        <v>251.751918850448</v>
       </c>
       <c r="D8">
-        <v>259.6065834253253</v>
+        <v>260.803918850448</v>
       </c>
       <c r="E8">
-        <v>-132.044</v>
+        <v>-129.668</v>
       </c>
       <c r="F8">
-        <v>14.256</v>
+        <v>16.632</v>
       </c>
       <c r="G8">
         <v>7.58</v>
@@ -2059,28 +2059,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M8">
-        <v>0.7170768</v>
+        <v>0.8365896</v>
       </c>
       <c r="N8">
-        <v>59.04958986666666</v>
+        <v>58.93007706666666</v>
       </c>
       <c r="O8">
-        <v>20.66735645333333</v>
+        <v>20.62552697333333</v>
       </c>
       <c r="P8">
-        <v>38.38223341333334</v>
+        <v>38.30455009333333</v>
       </c>
       <c r="Q8">
-        <v>63.78223341333334</v>
+        <v>63.70455009333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1868179909987245</v>
+        <v>0.1878247423925009</v>
       </c>
       <c r="T8">
-        <v>0.6928738745819318</v>
+        <v>0.6978204188774961</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>83.34765072118728</v>
+        <v>71.44084347530337</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1769656604250259</v>
+        <v>0.1763607093112508</v>
       </c>
       <c r="C9">
-        <v>251.751918850448</v>
+        <v>250.5843499475046</v>
       </c>
       <c r="D9">
-        <v>260.803918850448</v>
+        <v>262.0123499475047</v>
       </c>
       <c r="E9">
-        <v>-129.668</v>
+        <v>-127.292</v>
       </c>
       <c r="F9">
-        <v>16.632</v>
+        <v>19.008</v>
       </c>
       <c r="G9">
         <v>7.58</v>
@@ -2141,28 +2141,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M9">
-        <v>0.8365896</v>
+        <v>0.9561024000000001</v>
       </c>
       <c r="N9">
-        <v>58.93007706666666</v>
+        <v>58.81056426666667</v>
       </c>
       <c r="O9">
-        <v>20.62552697333333</v>
+        <v>20.58369749333333</v>
       </c>
       <c r="P9">
-        <v>38.30455009333333</v>
+        <v>38.22686677333333</v>
       </c>
       <c r="Q9">
-        <v>63.70455009333334</v>
+        <v>63.62686677333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1878247423925009</v>
+        <v>0.1888533796861422</v>
       </c>
       <c r="T9">
-        <v>0.6978204188774961</v>
+        <v>0.7028744967447033</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>71.44084347530337</v>
+        <v>62.51073804089045</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1763607093112508</v>
+        <v>0.1757557581974757</v>
       </c>
       <c r="C10">
-        <v>250.5843499475046</v>
+        <v>249.4280316693619</v>
       </c>
       <c r="D10">
-        <v>262.0123499475047</v>
+        <v>263.2320316693619</v>
       </c>
       <c r="E10">
-        <v>-127.292</v>
+        <v>-124.916</v>
       </c>
       <c r="F10">
-        <v>19.008</v>
+        <v>21.384</v>
       </c>
       <c r="G10">
         <v>7.58</v>
@@ -2223,28 +2223,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M10">
-        <v>0.9561024000000001</v>
+        <v>1.0756152</v>
       </c>
       <c r="N10">
-        <v>58.81056426666667</v>
+        <v>58.69105146666666</v>
       </c>
       <c r="O10">
-        <v>20.58369749333333</v>
+        <v>20.54186801333333</v>
       </c>
       <c r="P10">
-        <v>38.22686677333333</v>
+        <v>38.14918345333334</v>
       </c>
       <c r="Q10">
-        <v>63.62686677333333</v>
+        <v>63.54918345333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1888533796861422</v>
+        <v>0.1899046243928305</v>
       </c>
       <c r="T10">
-        <v>0.7028744967447033</v>
+        <v>0.7080396532463546</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.51073804089045</v>
+        <v>55.56510048079152</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1757557581974757</v>
+        <v>0.1751508070837006</v>
       </c>
       <c r="C11">
-        <v>249.4280316693619</v>
+        <v>248.2831218676365</v>
       </c>
       <c r="D11">
-        <v>263.2320316693619</v>
+        <v>264.4631218676365</v>
       </c>
       <c r="E11">
-        <v>-124.916</v>
+        <v>-122.54</v>
       </c>
       <c r="F11">
-        <v>21.384</v>
+        <v>23.76</v>
       </c>
       <c r="G11">
         <v>7.58</v>
@@ -2305,28 +2305,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M11">
-        <v>1.0756152</v>
+        <v>1.195128</v>
       </c>
       <c r="N11">
-        <v>58.69105146666666</v>
+        <v>58.57153866666667</v>
       </c>
       <c r="O11">
-        <v>20.54186801333333</v>
+        <v>20.50003853333333</v>
       </c>
       <c r="P11">
-        <v>38.14918345333334</v>
+        <v>38.07150013333334</v>
       </c>
       <c r="Q11">
-        <v>63.54918345333334</v>
+        <v>63.47150013333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1899046243928305</v>
+        <v>0.1909792300930007</v>
       </c>
       <c r="T11">
-        <v>0.7080396532463546</v>
+        <v>0.7133195910035981</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.56510048079152</v>
+        <v>50.00859043271237</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1751508070837006</v>
+        <v>0.1745458559699256</v>
       </c>
       <c r="C12">
-        <v>248.2831218676365</v>
+        <v>247.1497813607982</v>
       </c>
       <c r="D12">
-        <v>264.4631218676365</v>
+        <v>265.7057813607982</v>
       </c>
       <c r="E12">
-        <v>-122.54</v>
+        <v>-120.164</v>
       </c>
       <c r="F12">
-        <v>23.76000000000001</v>
+        <v>26.136</v>
       </c>
       <c r="G12">
         <v>7.58</v>
@@ -2387,28 +2387,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M12">
-        <v>1.195128</v>
+        <v>1.3146408</v>
       </c>
       <c r="N12">
-        <v>58.57153866666667</v>
+        <v>58.45202586666667</v>
       </c>
       <c r="O12">
-        <v>20.50003853333333</v>
+        <v>20.45820905333333</v>
       </c>
       <c r="P12">
-        <v>38.07150013333334</v>
+        <v>37.99381681333334</v>
       </c>
       <c r="Q12">
-        <v>63.47150013333334</v>
+        <v>63.39381681333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1909792300930007</v>
+        <v>0.1920779842358714</v>
       </c>
       <c r="T12">
-        <v>0.7133195910035981</v>
+        <v>0.7187181790475213</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.00859043271236</v>
+        <v>45.46235493882942</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1745458559699256</v>
+        <v>0.1739409048561505</v>
       </c>
       <c r="C13">
-        <v>247.1497813607982</v>
+        <v>246.0281740042022</v>
       </c>
       <c r="D13">
-        <v>265.7057813607982</v>
+        <v>266.9601740042023</v>
       </c>
       <c r="E13">
-        <v>-120.164</v>
+        <v>-117.788</v>
       </c>
       <c r="F13">
-        <v>26.136</v>
+        <v>28.512</v>
       </c>
       <c r="G13">
         <v>7.58</v>
@@ -2469,28 +2469,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M13">
-        <v>1.3146408</v>
+        <v>1.4341536</v>
       </c>
       <c r="N13">
-        <v>58.45202586666667</v>
+        <v>58.33251306666666</v>
       </c>
       <c r="O13">
-        <v>20.45820905333333</v>
+        <v>20.41637957333333</v>
       </c>
       <c r="P13">
-        <v>37.99381681333334</v>
+        <v>37.91613349333333</v>
       </c>
       <c r="Q13">
-        <v>63.39381681333334</v>
+        <v>63.31613349333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1920779842358714</v>
+        <v>0.1932017100638074</v>
       </c>
       <c r="T13">
-        <v>0.7187181790475213</v>
+        <v>0.7242394622742608</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.46235493882942</v>
+        <v>41.67382536059364</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1739409048561505</v>
+        <v>0.1733359537423754</v>
       </c>
       <c r="C14">
-        <v>246.0281740042022</v>
+        <v>244.9184667621147</v>
       </c>
       <c r="D14">
-        <v>266.9601740042023</v>
+        <v>268.2264667621147</v>
       </c>
       <c r="E14">
-        <v>-117.788</v>
+        <v>-115.412</v>
       </c>
       <c r="F14">
-        <v>28.512</v>
+        <v>30.88800000000001</v>
       </c>
       <c r="G14">
         <v>7.58</v>
@@ -2551,28 +2551,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M14">
-        <v>1.4341536</v>
+        <v>1.5536664</v>
       </c>
       <c r="N14">
-        <v>58.33251306666666</v>
+        <v>58.21300026666667</v>
       </c>
       <c r="O14">
-        <v>20.41637957333333</v>
+        <v>20.37455009333333</v>
       </c>
       <c r="P14">
-        <v>37.91613349333333</v>
+        <v>37.83845017333334</v>
       </c>
       <c r="Q14">
-        <v>63.31613349333334</v>
+        <v>63.23845017333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1932017100638074</v>
+        <v>0.194351268669397</v>
       </c>
       <c r="T14">
-        <v>0.7242394622742608</v>
+        <v>0.7298876715521898</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.67382536059364</v>
+        <v>38.46814648670182</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1733359537423754</v>
+        <v>0.1727310026286004</v>
       </c>
       <c r="C15">
-        <v>244.9184667621147</v>
+        <v>243.8208297817978</v>
       </c>
       <c r="D15">
-        <v>268.2264667621147</v>
+        <v>269.5048297817978</v>
       </c>
       <c r="E15">
-        <v>-115.412</v>
+        <v>-113.036</v>
       </c>
       <c r="F15">
-        <v>30.88800000000001</v>
+        <v>33.264</v>
       </c>
       <c r="G15">
         <v>7.58</v>
@@ -2633,28 +2633,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M15">
-        <v>1.5536664</v>
+        <v>1.6731792</v>
       </c>
       <c r="N15">
-        <v>58.21300026666667</v>
+        <v>58.09348746666667</v>
       </c>
       <c r="O15">
-        <v>20.37455009333333</v>
+        <v>20.33272061333333</v>
       </c>
       <c r="P15">
-        <v>37.83845017333334</v>
+        <v>37.76076685333334</v>
       </c>
       <c r="Q15">
-        <v>63.23845017333333</v>
+        <v>63.16076685333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.194351268669397</v>
+        <v>0.1955275611960469</v>
       </c>
       <c r="T15">
-        <v>0.7298876715521898</v>
+        <v>0.7356672345342568</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.46814648670182</v>
+        <v>35.72042173765169</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1727310026286004</v>
+        <v>0.1721260515148252</v>
       </c>
       <c r="C16">
-        <v>243.8208297817978</v>
+        <v>242.7354364697234</v>
       </c>
       <c r="D16">
-        <v>269.5048297817978</v>
+        <v>270.7954364697234</v>
       </c>
       <c r="E16">
-        <v>-113.036</v>
+        <v>-110.66</v>
       </c>
       <c r="F16">
-        <v>33.264</v>
+        <v>35.64000000000001</v>
       </c>
       <c r="G16">
         <v>7.58</v>
@@ -2715,28 +2715,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M16">
-        <v>1.6731792</v>
+        <v>1.792692</v>
       </c>
       <c r="N16">
-        <v>58.09348746666667</v>
+        <v>57.97397466666666</v>
       </c>
       <c r="O16">
-        <v>20.33272061333333</v>
+        <v>20.29089113333333</v>
       </c>
       <c r="P16">
-        <v>37.76076685333334</v>
+        <v>37.68308353333333</v>
       </c>
       <c r="Q16">
-        <v>63.16076685333334</v>
+        <v>63.08308353333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1955275611960469</v>
+        <v>0.1967315311939121</v>
       </c>
       <c r="T16">
-        <v>0.7356672345342568</v>
+        <v>0.7415827872335488</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.72042173765169</v>
+        <v>33.3390602884749</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1721260515148252</v>
+        <v>0.1715211004010502</v>
       </c>
       <c r="C17">
-        <v>242.7354364697234</v>
+        <v>241.6624635699873</v>
       </c>
       <c r="D17">
-        <v>270.7954364697234</v>
+        <v>272.0984635699873</v>
       </c>
       <c r="E17">
-        <v>-110.66</v>
+        <v>-108.284</v>
       </c>
       <c r="F17">
-        <v>35.64</v>
+        <v>38.01600000000001</v>
       </c>
       <c r="G17">
         <v>7.58</v>
@@ -2797,28 +2797,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M17">
-        <v>1.792692</v>
+        <v>1.9122048</v>
       </c>
       <c r="N17">
-        <v>57.97397466666666</v>
+        <v>57.85446186666667</v>
       </c>
       <c r="O17">
-        <v>20.29089113333333</v>
+        <v>20.24906165333333</v>
       </c>
       <c r="P17">
-        <v>37.68308353333333</v>
+        <v>37.60540021333334</v>
       </c>
       <c r="Q17">
-        <v>63.08308353333334</v>
+        <v>63.00540021333335</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1967315311939121</v>
+        <v>0.1979641671441074</v>
       </c>
       <c r="T17">
-        <v>0.7415827872335488</v>
+        <v>0.7476391864256809</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.33906028847491</v>
+        <v>31.25536902044523</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1715211004010502</v>
+        <v>0.1709161492872751</v>
       </c>
       <c r="C18">
-        <v>241.6624635699873</v>
+        <v>240.6020912449983</v>
       </c>
       <c r="D18">
-        <v>272.0984635699873</v>
+        <v>273.4140912449984</v>
       </c>
       <c r="E18">
-        <v>-108.284</v>
+        <v>-105.908</v>
       </c>
       <c r="F18">
-        <v>38.01600000000001</v>
+        <v>40.39200000000001</v>
       </c>
       <c r="G18">
         <v>7.58</v>
@@ -2879,28 +2879,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M18">
-        <v>1.9122048</v>
+        <v>2.0317176</v>
       </c>
       <c r="N18">
-        <v>57.85446186666667</v>
+        <v>57.73494906666667</v>
       </c>
       <c r="O18">
-        <v>20.24906165333333</v>
+        <v>20.20723217333333</v>
       </c>
       <c r="P18">
-        <v>37.60540021333334</v>
+        <v>37.52771689333333</v>
       </c>
       <c r="Q18">
-        <v>63.00540021333335</v>
+        <v>62.92771689333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1979641671441074</v>
+        <v>0.1992265051653917</v>
       </c>
       <c r="T18">
-        <v>0.7476391864256809</v>
+        <v>0.7538415229477441</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.25536902044523</v>
+        <v>29.4168179015955</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1709161492872751</v>
+        <v>0.1703111981735</v>
       </c>
       <c r="C19">
-        <v>240.6020912449983</v>
+        <v>239.5545031585195</v>
       </c>
       <c r="D19">
-        <v>273.4140912449984</v>
+        <v>274.7425031585195</v>
       </c>
       <c r="E19">
-        <v>-105.908</v>
+        <v>-103.532</v>
       </c>
       <c r="F19">
-        <v>40.39200000000001</v>
+        <v>42.76800000000001</v>
       </c>
       <c r="G19">
         <v>7.58</v>
@@ -2961,28 +2961,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M19">
-        <v>2.0317176</v>
+        <v>2.1512304</v>
       </c>
       <c r="N19">
-        <v>57.73494906666667</v>
+        <v>57.61543626666666</v>
       </c>
       <c r="O19">
-        <v>20.20723217333333</v>
+        <v>20.16540269333333</v>
       </c>
       <c r="P19">
-        <v>37.52771689333333</v>
+        <v>37.45003357333333</v>
       </c>
       <c r="Q19">
-        <v>62.92771689333334</v>
+        <v>62.85003357333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1992265051653917</v>
+        <v>0.2005196319189024</v>
       </c>
       <c r="T19">
-        <v>0.7538415229477441</v>
+        <v>0.7601951359703453</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.4168179015955</v>
+        <v>27.78255024039576</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1703111981735</v>
+        <v>0.169706247059725</v>
       </c>
       <c r="C20">
-        <v>239.5545031585195</v>
+        <v>238.5198865611414</v>
       </c>
       <c r="D20">
-        <v>274.7425031585195</v>
+        <v>276.0838865611414</v>
       </c>
       <c r="E20">
-        <v>-103.532</v>
+        <v>-101.156</v>
       </c>
       <c r="F20">
-        <v>42.768</v>
+        <v>45.14400000000001</v>
       </c>
       <c r="G20">
         <v>7.58</v>
@@ -3043,28 +3043,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M20">
-        <v>2.1512304</v>
+        <v>2.2707432</v>
       </c>
       <c r="N20">
-        <v>57.61543626666666</v>
+        <v>57.49592346666667</v>
       </c>
       <c r="O20">
-        <v>20.16540269333333</v>
+        <v>20.12357321333333</v>
       </c>
       <c r="P20">
-        <v>37.45003357333333</v>
+        <v>37.37235025333334</v>
       </c>
       <c r="Q20">
-        <v>62.85003357333333</v>
+        <v>62.77235025333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2005196319189024</v>
+        <v>0.2018446877280555</v>
       </c>
       <c r="T20">
-        <v>0.7601951359703453</v>
+        <v>0.7667056283268381</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.78255024039576</v>
+        <v>26.32031075405914</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.169706247059725</v>
+        <v>0.1691012959459499</v>
       </c>
       <c r="C21">
-        <v>238.5198865611414</v>
+        <v>237.4984323782732</v>
       </c>
       <c r="D21">
-        <v>276.0838865611414</v>
+        <v>277.4384323782733</v>
       </c>
       <c r="E21">
-        <v>-101.156</v>
+        <v>-98.78</v>
       </c>
       <c r="F21">
-        <v>45.14400000000001</v>
+        <v>47.52000000000001</v>
       </c>
       <c r="G21">
         <v>7.58</v>
@@ -3125,28 +3125,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M21">
-        <v>2.2707432</v>
+        <v>2.390256</v>
       </c>
       <c r="N21">
-        <v>57.49592346666667</v>
+        <v>57.37641066666666</v>
       </c>
       <c r="O21">
-        <v>20.12357321333333</v>
+        <v>20.08174373333333</v>
       </c>
       <c r="P21">
-        <v>37.37235025333334</v>
+        <v>37.29466693333333</v>
       </c>
       <c r="Q21">
-        <v>62.77235025333334</v>
+        <v>62.69466693333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2018446877280555</v>
+        <v>0.2032028699324373</v>
       </c>
       <c r="T21">
-        <v>0.7667056283268381</v>
+        <v>0.7733788829922431</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.32031075405914</v>
+        <v>25.00429521635618</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1691012959459499</v>
+        <v>0.1684963448321748</v>
       </c>
       <c r="C22">
-        <v>237.4984323782732</v>
+        <v>236.4903353007344</v>
       </c>
       <c r="D22">
-        <v>277.4384323782733</v>
+        <v>278.8063353007345</v>
       </c>
       <c r="E22">
-        <v>-98.78</v>
+        <v>-96.404</v>
       </c>
       <c r="F22">
-        <v>47.52000000000001</v>
+        <v>49.89600000000001</v>
       </c>
       <c r="G22">
         <v>7.58</v>
@@ -3207,28 +3207,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M22">
-        <v>2.390256</v>
+        <v>2.5097688</v>
       </c>
       <c r="N22">
-        <v>57.37641066666666</v>
+        <v>57.25689786666666</v>
       </c>
       <c r="O22">
-        <v>20.08174373333333</v>
+        <v>20.03991425333333</v>
       </c>
       <c r="P22">
-        <v>37.29466693333333</v>
+        <v>37.21698361333333</v>
       </c>
       <c r="Q22">
-        <v>62.69466693333334</v>
+        <v>62.61698361333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2032028699324373</v>
+        <v>0.2045954364964238</v>
       </c>
       <c r="T22">
-        <v>0.7733788829922431</v>
+        <v>0.7802210808137343</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.00429521635618</v>
+        <v>23.81361449176779</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1684963448321748</v>
+        <v>0.1678913937183997</v>
       </c>
       <c r="C23">
-        <v>236.4903353007344</v>
+        <v>235.4957938780422</v>
       </c>
       <c r="D23">
-        <v>278.8063353007345</v>
+        <v>280.1877938780422</v>
       </c>
       <c r="E23">
-        <v>-96.40400000000001</v>
+        <v>-94.02800000000001</v>
       </c>
       <c r="F23">
-        <v>49.896</v>
+        <v>52.27200000000001</v>
       </c>
       <c r="G23">
         <v>7.58</v>
@@ -3289,28 +3289,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M23">
-        <v>2.5097688</v>
+        <v>2.6292816</v>
       </c>
       <c r="N23">
-        <v>57.25689786666666</v>
+        <v>57.13738506666667</v>
       </c>
       <c r="O23">
-        <v>20.03991425333333</v>
+        <v>19.99808477333333</v>
       </c>
       <c r="P23">
-        <v>37.21698361333333</v>
+        <v>37.13930029333333</v>
       </c>
       <c r="Q23">
-        <v>62.61698361333333</v>
+        <v>62.53930029333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2045954364964238</v>
+        <v>0.2060237098953842</v>
       </c>
       <c r="T23">
-        <v>0.7802210808137343</v>
+        <v>0.7872387196050072</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.81361449176779</v>
+        <v>22.73117746941471</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1678913937183997</v>
+        <v>0.1672864426046246</v>
       </c>
       <c r="C24">
-        <v>235.4957938780422</v>
+        <v>234.5150106144835</v>
       </c>
       <c r="D24">
-        <v>280.1877938780422</v>
+        <v>281.5830106144836</v>
       </c>
       <c r="E24">
-        <v>-94.02800000000001</v>
+        <v>-91.652</v>
       </c>
       <c r="F24">
-        <v>52.27200000000001</v>
+        <v>54.64800000000001</v>
       </c>
       <c r="G24">
         <v>7.58</v>
@@ -3371,28 +3371,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M24">
-        <v>2.6292816</v>
+        <v>2.7487944</v>
       </c>
       <c r="N24">
-        <v>57.13738506666667</v>
+        <v>57.01787226666666</v>
       </c>
       <c r="O24">
-        <v>19.99808477333333</v>
+        <v>19.95625529333333</v>
       </c>
       <c r="P24">
-        <v>37.13930029333333</v>
+        <v>37.06161697333333</v>
       </c>
       <c r="Q24">
-        <v>62.53930029333334</v>
+        <v>62.46161697333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2060237098953842</v>
+        <v>0.2074890813047073</v>
       </c>
       <c r="T24">
-        <v>0.7872387196050072</v>
+        <v>0.7944386347285212</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.73117746941471</v>
+        <v>21.74286540552711</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1672864426046246</v>
+        <v>0.1666814914908495</v>
       </c>
       <c r="C25">
-        <v>234.5150106144835</v>
+        <v>233.548192068075</v>
       </c>
       <c r="D25">
-        <v>281.5830106144836</v>
+        <v>282.992192068075</v>
       </c>
       <c r="E25">
-        <v>-91.652</v>
+        <v>-89.27600000000001</v>
       </c>
       <c r="F25">
-        <v>54.64800000000001</v>
+        <v>57.02400000000001</v>
       </c>
       <c r="G25">
         <v>7.58</v>
@@ -3453,28 +3453,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M25">
-        <v>2.7487944</v>
+        <v>2.8683072</v>
       </c>
       <c r="N25">
-        <v>57.01787226666666</v>
+        <v>56.89835946666666</v>
       </c>
       <c r="O25">
-        <v>19.95625529333333</v>
+        <v>19.91442581333333</v>
       </c>
       <c r="P25">
-        <v>37.06161697333333</v>
+        <v>36.98393365333333</v>
       </c>
       <c r="Q25">
-        <v>62.46161697333334</v>
+        <v>62.38393365333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2074890813047073</v>
+        <v>0.2089930151195389</v>
       </c>
       <c r="T25">
-        <v>0.7944386347285212</v>
+        <v>0.8018280213026537</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.74286540552711</v>
+        <v>20.83691268029682</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1666814914908495</v>
+        <v>0.1660765403770745</v>
       </c>
       <c r="C26">
-        <v>233.548192068075</v>
+        <v>232.5955489525058</v>
       </c>
       <c r="D26">
-        <v>282.992192068075</v>
+        <v>284.4155489525058</v>
       </c>
       <c r="E26">
-        <v>-89.27600000000001</v>
+        <v>-86.90000000000001</v>
       </c>
       <c r="F26">
-        <v>57.024</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="G26">
         <v>7.58</v>
@@ -3535,28 +3535,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M26">
-        <v>2.8683072</v>
+        <v>2.98782</v>
       </c>
       <c r="N26">
-        <v>56.89835946666667</v>
+        <v>56.77884666666667</v>
       </c>
       <c r="O26">
-        <v>19.91442581333333</v>
+        <v>19.87259633333333</v>
       </c>
       <c r="P26">
-        <v>36.98393365333334</v>
+        <v>36.90625033333333</v>
       </c>
       <c r="Q26">
-        <v>62.38393365333334</v>
+        <v>62.30625033333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2089930151195389</v>
+        <v>0.2105370538360993</v>
       </c>
       <c r="T26">
-        <v>0.8018280213026537</v>
+        <v>0.8094144581854301</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.83691268029682</v>
+        <v>20.00343617308495</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1660765403770745</v>
+        <v>0.1654715892632994</v>
       </c>
       <c r="C27">
-        <v>232.5955489525058</v>
+        <v>231.6572962421755</v>
       </c>
       <c r="D27">
-        <v>284.4155489525058</v>
+        <v>285.8532962421755</v>
       </c>
       <c r="E27">
-        <v>-86.90000000000001</v>
+        <v>-84.524</v>
       </c>
       <c r="F27">
-        <v>59.40000000000001</v>
+        <v>61.77600000000001</v>
       </c>
       <c r="G27">
         <v>7.58</v>
@@ -3617,28 +3617,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M27">
-        <v>2.98782</v>
+        <v>3.1073328</v>
       </c>
       <c r="N27">
-        <v>56.77884666666667</v>
+        <v>56.65933386666666</v>
       </c>
       <c r="O27">
-        <v>19.87259633333333</v>
+        <v>19.83076685333333</v>
       </c>
       <c r="P27">
-        <v>36.90625033333333</v>
+        <v>36.82856701333333</v>
       </c>
       <c r="Q27">
-        <v>62.30625033333334</v>
+        <v>62.22856701333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2105370538360993</v>
+        <v>0.2121228233287829</v>
       </c>
       <c r="T27">
-        <v>0.8094144581854301</v>
+        <v>0.8172059339028759</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.00343617308495</v>
+        <v>19.23407324335091</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1654715892632994</v>
+        <v>0.1648666381495243</v>
       </c>
       <c r="C28">
-        <v>231.6572962421755</v>
+        <v>230.7336532804319</v>
       </c>
       <c r="D28">
-        <v>285.8532962421755</v>
+        <v>287.3056532804319</v>
       </c>
       <c r="E28">
-        <v>-84.524</v>
+        <v>-82.148</v>
       </c>
       <c r="F28">
-        <v>61.77600000000001</v>
+        <v>64.15200000000002</v>
       </c>
       <c r="G28">
         <v>7.58</v>
@@ -3699,28 +3699,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M28">
-        <v>3.1073328</v>
+        <v>3.226845600000001</v>
       </c>
       <c r="N28">
-        <v>56.65933386666666</v>
+        <v>56.53982106666666</v>
       </c>
       <c r="O28">
-        <v>19.83076685333333</v>
+        <v>19.78893737333333</v>
       </c>
       <c r="P28">
-        <v>36.82856701333333</v>
+        <v>36.75088369333334</v>
       </c>
       <c r="Q28">
-        <v>62.22856701333333</v>
+        <v>62.15088369333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2121228233287829</v>
+        <v>0.2137520385609922</v>
       </c>
       <c r="T28">
-        <v>0.8172059339028759</v>
+        <v>0.8252108747084709</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.23407324335091</v>
+        <v>18.52170016026383</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1648666381495243</v>
+        <v>0.1642616870357492</v>
       </c>
       <c r="C29">
-        <v>230.7336532804319</v>
+        <v>229.8248438911262</v>
       </c>
       <c r="D29">
-        <v>287.3056532804319</v>
+        <v>288.7728438911262</v>
       </c>
       <c r="E29">
-        <v>-82.148</v>
+        <v>-79.77200000000001</v>
       </c>
       <c r="F29">
-        <v>64.15200000000002</v>
+        <v>66.52800000000001</v>
       </c>
       <c r="G29">
         <v>7.58</v>
@@ -3781,28 +3781,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M29">
-        <v>3.226845600000001</v>
+        <v>3.3463584</v>
       </c>
       <c r="N29">
-        <v>56.53982106666666</v>
+        <v>56.42030826666667</v>
       </c>
       <c r="O29">
-        <v>19.78893737333333</v>
+        <v>19.74710789333333</v>
       </c>
       <c r="P29">
-        <v>36.75088369333334</v>
+        <v>36.67320037333333</v>
       </c>
       <c r="Q29">
-        <v>62.15088369333334</v>
+        <v>62.07320037333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2137520385609922</v>
+        <v>0.2154265097718739</v>
       </c>
       <c r="T29">
-        <v>0.8252108747084709</v>
+        <v>0.833438174980888</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.52170016026383</v>
+        <v>17.86021086882585</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1642616870357492</v>
+        <v>0.1636567359219741</v>
       </c>
       <c r="C30">
-        <v>229.8248438911262</v>
+        <v>228.9310964936045</v>
       </c>
       <c r="D30">
-        <v>288.7728438911262</v>
+        <v>290.2550964936045</v>
       </c>
       <c r="E30">
-        <v>-79.77200000000001</v>
+        <v>-77.396</v>
       </c>
       <c r="F30">
-        <v>66.52800000000001</v>
+        <v>68.90400000000001</v>
       </c>
       <c r="G30">
         <v>7.58</v>
@@ -3863,28 +3863,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M30">
-        <v>3.3463584</v>
+        <v>3.4658712</v>
       </c>
       <c r="N30">
-        <v>56.42030826666667</v>
+        <v>56.30079546666666</v>
       </c>
       <c r="O30">
-        <v>19.74710789333333</v>
+        <v>19.70527841333333</v>
       </c>
       <c r="P30">
-        <v>36.67320037333333</v>
+        <v>36.59551705333333</v>
       </c>
       <c r="Q30">
-        <v>62.07320037333334</v>
+        <v>61.99551705333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2154265097718739</v>
+        <v>0.2171481491858791</v>
       </c>
       <c r="T30">
-        <v>0.833438174980888</v>
+        <v>0.8418972301905563</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.86021086882585</v>
+        <v>17.2443415285215</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1636567359219741</v>
+        <v>0.163051784808199</v>
       </c>
       <c r="C31">
-        <v>228.9310964936045</v>
+        <v>228.0526442212569</v>
       </c>
       <c r="D31">
-        <v>290.2550964936045</v>
+        <v>291.7526442212569</v>
       </c>
       <c r="E31">
-        <v>-77.39600000000002</v>
+        <v>-75.02000000000001</v>
       </c>
       <c r="F31">
-        <v>68.904</v>
+        <v>71.28</v>
       </c>
       <c r="G31">
         <v>7.58</v>
@@ -3945,28 +3945,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M31">
-        <v>3.4658712</v>
+        <v>3.585384</v>
       </c>
       <c r="N31">
-        <v>56.30079546666666</v>
+        <v>56.18128266666667</v>
       </c>
       <c r="O31">
-        <v>19.70527841333333</v>
+        <v>19.66344893333333</v>
       </c>
       <c r="P31">
-        <v>36.59551705333333</v>
+        <v>36.51783373333333</v>
       </c>
       <c r="Q31">
-        <v>61.99551705333333</v>
+        <v>61.91783373333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2171481491858791</v>
+        <v>0.2189189782974272</v>
       </c>
       <c r="T31">
-        <v>0.8418972301905563</v>
+        <v>0.8505979726919293</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.24434152852151</v>
+        <v>16.66953014423746</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.163051784808199</v>
+        <v>0.162446833694424</v>
       </c>
       <c r="C32">
-        <v>228.0526442212569</v>
+        <v>227.1897250437576</v>
       </c>
       <c r="D32">
-        <v>291.7526442212569</v>
+        <v>293.2657250437576</v>
       </c>
       <c r="E32">
-        <v>-75.02000000000001</v>
+        <v>-72.64400000000001</v>
       </c>
       <c r="F32">
-        <v>71.28</v>
+        <v>73.65600000000001</v>
       </c>
       <c r="G32">
         <v>7.58</v>
@@ -4027,28 +4027,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M32">
-        <v>3.585384</v>
+        <v>3.7048968</v>
       </c>
       <c r="N32">
-        <v>56.18128266666667</v>
+        <v>56.06176986666667</v>
       </c>
       <c r="O32">
-        <v>19.66344893333333</v>
+        <v>19.62161945333333</v>
       </c>
       <c r="P32">
-        <v>36.51783373333333</v>
+        <v>36.44015041333333</v>
       </c>
       <c r="Q32">
-        <v>61.91783373333334</v>
+        <v>61.84015041333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2189189782974272</v>
+        <v>0.2207411357890203</v>
       </c>
       <c r="T32">
-        <v>0.8505979726919293</v>
+        <v>0.8595509106281249</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.66953014423746</v>
+        <v>16.13180336539109</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.162446833694424</v>
+        <v>0.1618418825806489</v>
       </c>
       <c r="C33">
-        <v>227.1897250437576</v>
+        <v>226.3425818931281</v>
       </c>
       <c r="D33">
-        <v>293.2657250437576</v>
+        <v>294.7945818931281</v>
       </c>
       <c r="E33">
-        <v>-72.64400000000001</v>
+        <v>-70.268</v>
       </c>
       <c r="F33">
-        <v>73.65600000000001</v>
+        <v>76.03200000000001</v>
       </c>
       <c r="G33">
         <v>7.58</v>
@@ -4109,28 +4109,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M33">
-        <v>3.7048968</v>
+        <v>3.824409600000001</v>
       </c>
       <c r="N33">
-        <v>56.06176986666667</v>
+        <v>55.94225706666666</v>
       </c>
       <c r="O33">
-        <v>19.62161945333333</v>
+        <v>19.57978997333333</v>
       </c>
       <c r="P33">
-        <v>36.44015041333333</v>
+        <v>36.36246709333334</v>
       </c>
       <c r="Q33">
-        <v>61.84015041333333</v>
+        <v>61.76246709333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2207411357890203</v>
+        <v>0.2226168861480131</v>
       </c>
       <c r="T33">
-        <v>0.8595509106281249</v>
+        <v>0.8687671702683262</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.13180336539109</v>
+        <v>15.62768451022261</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1618418825806489</v>
+        <v>0.1612369314668738</v>
       </c>
       <c r="C34">
-        <v>226.3425818931281</v>
+        <v>225.5114627937634</v>
       </c>
       <c r="D34">
-        <v>294.7945818931281</v>
+        <v>296.3394627937635</v>
       </c>
       <c r="E34">
-        <v>-70.268</v>
+        <v>-67.892</v>
       </c>
       <c r="F34">
-        <v>76.03200000000001</v>
+        <v>78.40800000000002</v>
       </c>
       <c r="G34">
         <v>7.58</v>
@@ -4191,28 +4191,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M34">
-        <v>3.824409600000001</v>
+        <v>3.9439224</v>
       </c>
       <c r="N34">
-        <v>55.94225706666666</v>
+        <v>55.82274426666667</v>
       </c>
       <c r="O34">
-        <v>19.57978997333333</v>
+        <v>19.53796049333333</v>
       </c>
       <c r="P34">
-        <v>36.36246709333334</v>
+        <v>36.28478377333333</v>
       </c>
       <c r="Q34">
-        <v>61.76246709333334</v>
+        <v>61.68478377333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2226168861480131</v>
+        <v>0.2245486290550355</v>
       </c>
       <c r="T34">
-        <v>0.8687671702683262</v>
+        <v>0.8782585421365932</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.62768451022261</v>
+        <v>15.15411831294314</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1612369314668738</v>
+        <v>0.1606319803530987</v>
       </c>
       <c r="C35">
-        <v>225.5114627937634</v>
+        <v>224.6966209965686</v>
       </c>
       <c r="D35">
-        <v>296.3394627937635</v>
+        <v>297.9006209965686</v>
       </c>
       <c r="E35">
-        <v>-67.892</v>
+        <v>-65.51599999999999</v>
       </c>
       <c r="F35">
-        <v>78.40800000000002</v>
+        <v>80.78400000000002</v>
       </c>
       <c r="G35">
         <v>7.58</v>
@@ -4273,28 +4273,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M35">
-        <v>3.9439224</v>
+        <v>4.063435200000001</v>
       </c>
       <c r="N35">
-        <v>55.82274426666667</v>
+        <v>55.70323146666667</v>
       </c>
       <c r="O35">
-        <v>19.53796049333333</v>
+        <v>19.49613101333333</v>
       </c>
       <c r="P35">
-        <v>36.28478377333333</v>
+        <v>36.20710045333333</v>
       </c>
       <c r="Q35">
-        <v>61.68478377333334</v>
+        <v>61.60710045333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2245486290550355</v>
+        <v>0.2265389096259072</v>
       </c>
       <c r="T35">
-        <v>0.8782585421365932</v>
+        <v>0.8880375313342016</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.15411831294314</v>
+        <v>14.70840895079775</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1606319803530987</v>
+        <v>0.1600270292393237</v>
       </c>
       <c r="C36">
-        <v>224.6966209965686</v>
+        <v>223.8983151173582</v>
       </c>
       <c r="D36">
-        <v>297.9006209965686</v>
+        <v>299.4783151173582</v>
       </c>
       <c r="E36">
-        <v>-65.51599999999999</v>
+        <v>-63.14</v>
       </c>
       <c r="F36">
-        <v>80.78400000000002</v>
+        <v>83.16000000000001</v>
       </c>
       <c r="G36">
         <v>7.58</v>
@@ -4355,28 +4355,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M36">
-        <v>4.063435200000001</v>
+        <v>4.182948000000001</v>
       </c>
       <c r="N36">
-        <v>55.70323146666667</v>
+        <v>55.58371866666666</v>
       </c>
       <c r="O36">
-        <v>19.49613101333333</v>
+        <v>19.45430153333333</v>
       </c>
       <c r="P36">
-        <v>36.20710045333333</v>
+        <v>36.12941713333333</v>
       </c>
       <c r="Q36">
-        <v>61.60710045333333</v>
+        <v>61.52941713333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2265389096259072</v>
+        <v>0.2285904295989595</v>
       </c>
       <c r="T36">
-        <v>0.8880375313342016</v>
+        <v>0.8981174125071211</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.70840895079775</v>
+        <v>14.28816869506067</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1600270292393237</v>
+        <v>0.1594220781255486</v>
       </c>
       <c r="C37">
-        <v>223.8983151173582</v>
+        <v>223.1168092796772</v>
       </c>
       <c r="D37">
-        <v>299.4783151173582</v>
+        <v>301.0728092796772</v>
       </c>
       <c r="E37">
-        <v>-63.14</v>
+        <v>-60.764</v>
       </c>
       <c r="F37">
-        <v>83.16000000000001</v>
+        <v>85.53600000000002</v>
       </c>
       <c r="G37">
         <v>7.58</v>
@@ -4437,28 +4437,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M37">
-        <v>4.182948000000001</v>
+        <v>4.3024608</v>
       </c>
       <c r="N37">
-        <v>55.58371866666666</v>
+        <v>55.46420586666667</v>
       </c>
       <c r="O37">
-        <v>19.45430153333333</v>
+        <v>19.41247205333333</v>
       </c>
       <c r="P37">
-        <v>36.12941713333333</v>
+        <v>36.05173381333334</v>
       </c>
       <c r="Q37">
-        <v>61.52941713333334</v>
+        <v>61.45173381333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2285904295989595</v>
+        <v>0.2307060595711697</v>
       </c>
       <c r="T37">
-        <v>0.8981174125071211</v>
+        <v>0.9085122899666942</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.28816869506067</v>
+        <v>13.89127512019788</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1594220781255486</v>
+        <v>0.1588171270117735</v>
       </c>
       <c r="C38">
-        <v>223.1168092796771</v>
+        <v>222.3523732622066</v>
       </c>
       <c r="D38">
-        <v>301.0728092796771</v>
+        <v>302.6843732622066</v>
       </c>
       <c r="E38">
-        <v>-60.76400000000001</v>
+        <v>-58.38800000000001</v>
       </c>
       <c r="F38">
-        <v>85.536</v>
+        <v>87.91200000000001</v>
       </c>
       <c r="G38">
         <v>7.58</v>
@@ -4519,28 +4519,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M38">
-        <v>4.3024608</v>
+        <v>4.4219736</v>
       </c>
       <c r="N38">
-        <v>55.46420586666667</v>
+        <v>55.34469306666666</v>
       </c>
       <c r="O38">
-        <v>19.41247205333333</v>
+        <v>19.37064257333333</v>
       </c>
       <c r="P38">
-        <v>36.05173381333334</v>
+        <v>35.97405049333334</v>
       </c>
       <c r="Q38">
-        <v>61.45173381333333</v>
+        <v>61.37405049333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2307060595711697</v>
+        <v>0.2328888523996405</v>
       </c>
       <c r="T38">
-        <v>0.9085122899666942</v>
+        <v>0.919237163536095</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.89127512019788</v>
+        <v>13.51583525208442</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1588171270117735</v>
+        <v>0.1582121758979984</v>
       </c>
       <c r="C39">
-        <v>222.3523732622066</v>
+        <v>221.6052826509319</v>
       </c>
       <c r="D39">
-        <v>302.6843732622066</v>
+        <v>304.3132826509319</v>
       </c>
       <c r="E39">
-        <v>-58.38800000000001</v>
+        <v>-56.012</v>
       </c>
       <c r="F39">
-        <v>87.91200000000001</v>
+        <v>90.28800000000001</v>
       </c>
       <c r="G39">
         <v>7.58</v>
@@ -4601,28 +4601,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M39">
-        <v>4.4219736</v>
+        <v>4.5414864</v>
       </c>
       <c r="N39">
-        <v>55.34469306666666</v>
+        <v>55.22518026666667</v>
       </c>
       <c r="O39">
-        <v>19.37064257333333</v>
+        <v>19.32881309333333</v>
       </c>
       <c r="P39">
-        <v>35.97405049333334</v>
+        <v>35.89636717333333</v>
       </c>
       <c r="Q39">
-        <v>61.37405049333334</v>
+        <v>61.29636717333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2328888523996405</v>
+        <v>0.2351420578999975</v>
       </c>
       <c r="T39">
-        <v>0.919237163536095</v>
+        <v>0.930308000769025</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.51583525208442</v>
+        <v>13.16015537702957</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1582121758979984</v>
+        <v>0.1579874747842233</v>
       </c>
       <c r="C40">
-        <v>221.6052826509319</v>
+        <v>219.8387939504752</v>
       </c>
       <c r="D40">
-        <v>304.3132826509319</v>
+        <v>304.9227939504752</v>
       </c>
       <c r="E40">
-        <v>-56.012</v>
+        <v>-53.636</v>
       </c>
       <c r="F40">
-        <v>90.28800000000001</v>
+        <v>92.66400000000002</v>
       </c>
       <c r="G40">
         <v>7.58</v>
@@ -4683,45 +4683,45 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M40">
-        <v>4.5414864</v>
+        <v>4.799995200000001</v>
       </c>
       <c r="N40">
-        <v>55.22518026666667</v>
+        <v>54.96667146666667</v>
       </c>
       <c r="O40">
-        <v>19.32881309333333</v>
+        <v>19.23833501333333</v>
       </c>
       <c r="P40">
-        <v>35.89636717333333</v>
+        <v>35.72833645333333</v>
       </c>
       <c r="Q40">
-        <v>61.29636717333334</v>
+        <v>61.12833645333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2351420578999975</v>
+        <v>0.2374691389905301</v>
       </c>
       <c r="T40">
-        <v>0.930308000769025</v>
+        <v>0.9417418162718871</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>13.16015537702957</v>
+        <v>12.45140134029023</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1579874747842233</v>
+        <v>0.1573922736704483</v>
       </c>
       <c r="C41">
-        <v>219.8387939504752</v>
+        <v>219.0891644921375</v>
       </c>
       <c r="D41">
-        <v>304.9227939504752</v>
+        <v>306.5491644921375</v>
       </c>
       <c r="E41">
-        <v>-53.636</v>
+        <v>-51.25999999999999</v>
       </c>
       <c r="F41">
-        <v>92.66400000000002</v>
+        <v>95.04000000000002</v>
       </c>
       <c r="G41">
         <v>7.58</v>
@@ -4765,28 +4765,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M41">
-        <v>4.799995200000001</v>
+        <v>4.923072000000001</v>
       </c>
       <c r="N41">
-        <v>54.96667146666667</v>
+        <v>54.84359466666666</v>
       </c>
       <c r="O41">
-        <v>19.23833501333333</v>
+        <v>19.19525813333333</v>
       </c>
       <c r="P41">
-        <v>35.72833645333333</v>
+        <v>35.64833653333334</v>
       </c>
       <c r="Q41">
-        <v>61.12833645333333</v>
+        <v>61.04833653333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2374691389905301</v>
+        <v>0.2398737894507471</v>
       </c>
       <c r="T41">
-        <v>0.9417418162718871</v>
+        <v>0.9535567589581778</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.45140134029023</v>
+        <v>12.14011630678297</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1573922736704483</v>
+        <v>0.1567970725566732</v>
       </c>
       <c r="C42">
-        <v>219.0891644921375</v>
+        <v>218.3569772516081</v>
       </c>
       <c r="D42">
-        <v>306.5491644921375</v>
+        <v>308.1929772516081</v>
       </c>
       <c r="E42">
-        <v>-51.25999999999999</v>
+        <v>-48.884</v>
       </c>
       <c r="F42">
-        <v>95.04000000000002</v>
+        <v>97.41600000000001</v>
       </c>
       <c r="G42">
         <v>7.58</v>
@@ -4847,28 +4847,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M42">
-        <v>4.923072000000001</v>
+        <v>5.0461488</v>
       </c>
       <c r="N42">
-        <v>54.84359466666666</v>
+        <v>54.72051786666667</v>
       </c>
       <c r="O42">
-        <v>19.19525813333333</v>
+        <v>19.15218125333333</v>
       </c>
       <c r="P42">
-        <v>35.64833653333334</v>
+        <v>35.56833661333334</v>
       </c>
       <c r="Q42">
-        <v>61.04833653333334</v>
+        <v>60.96833661333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2398737894507471</v>
+        <v>0.2423599534858867</v>
       </c>
       <c r="T42">
-        <v>0.9535567589581778</v>
+        <v>0.9657722081762073</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.14011630678297</v>
+        <v>11.84401590905656</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1567970725566732</v>
+        <v>0.1562018714428981</v>
       </c>
       <c r="C43">
-        <v>218.3569772516081</v>
+        <v>217.6425143335469</v>
       </c>
       <c r="D43">
-        <v>308.1929772516081</v>
+        <v>309.8545143335469</v>
       </c>
       <c r="E43">
-        <v>-48.884</v>
+        <v>-46.508</v>
       </c>
       <c r="F43">
-        <v>97.41600000000001</v>
+        <v>99.79200000000002</v>
       </c>
       <c r="G43">
         <v>7.58</v>
@@ -4929,28 +4929,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M43">
-        <v>5.0461488</v>
+        <v>5.169225600000001</v>
       </c>
       <c r="N43">
-        <v>54.72051786666667</v>
+        <v>54.59744106666666</v>
       </c>
       <c r="O43">
-        <v>19.15218125333333</v>
+        <v>19.10910437333333</v>
       </c>
       <c r="P43">
-        <v>35.56833661333334</v>
+        <v>35.48833669333333</v>
       </c>
       <c r="Q43">
-        <v>60.96833661333334</v>
+        <v>60.88833669333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2423599534858867</v>
+        <v>0.2449318473153415</v>
       </c>
       <c r="T43">
-        <v>0.9657722081762073</v>
+        <v>0.9784088797810654</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.84401590905656</v>
+        <v>11.5620155302695</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1562018714428981</v>
+        <v>0.155606670329123</v>
       </c>
       <c r="C44">
-        <v>217.6425143335468</v>
+        <v>216.9460639591459</v>
       </c>
       <c r="D44">
-        <v>309.8545143335468</v>
+        <v>311.5340639591459</v>
       </c>
       <c r="E44">
-        <v>-46.50800000000001</v>
+        <v>-44.13200000000001</v>
       </c>
       <c r="F44">
-        <v>99.792</v>
+        <v>102.168</v>
       </c>
       <c r="G44">
         <v>7.58</v>
@@ -5011,28 +5011,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M44">
-        <v>5.1692256</v>
+        <v>5.292302400000001</v>
       </c>
       <c r="N44">
-        <v>54.59744106666667</v>
+        <v>54.47436426666667</v>
       </c>
       <c r="O44">
-        <v>19.10910437333333</v>
+        <v>19.06602749333333</v>
       </c>
       <c r="P44">
-        <v>35.48833669333334</v>
+        <v>35.40833677333333</v>
       </c>
       <c r="Q44">
-        <v>60.88833669333334</v>
+        <v>60.80833677333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2449318473153415</v>
+        <v>0.2475939830335492</v>
       </c>
       <c r="T44">
-        <v>0.9784088797810654</v>
+        <v>0.9914889433720588</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.5620155302695</v>
+        <v>11.29313144817021</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.155606670329123</v>
+        <v>0.1550114692153479</v>
       </c>
       <c r="C45">
-        <v>216.9460639591459</v>
+        <v>216.2679206328048</v>
       </c>
       <c r="D45">
-        <v>311.5340639591459</v>
+        <v>313.2319206328049</v>
       </c>
       <c r="E45">
-        <v>-44.13200000000001</v>
+        <v>-41.756</v>
       </c>
       <c r="F45">
-        <v>102.168</v>
+        <v>104.544</v>
       </c>
       <c r="G45">
         <v>7.58</v>
@@ -5093,28 +5093,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M45">
-        <v>5.292302400000001</v>
+        <v>5.4153792</v>
       </c>
       <c r="N45">
-        <v>54.47436426666667</v>
+        <v>54.35128746666666</v>
       </c>
       <c r="O45">
-        <v>19.06602749333333</v>
+        <v>19.02295061333333</v>
       </c>
       <c r="P45">
-        <v>35.40833677333333</v>
+        <v>35.32833685333333</v>
       </c>
       <c r="Q45">
-        <v>60.80833677333334</v>
+        <v>60.72833685333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2475939830335492</v>
+        <v>0.250351195027407</v>
       </c>
       <c r="T45">
-        <v>0.9914889433720588</v>
+        <v>1.005036152091302</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.29313144817021</v>
+        <v>11.0364693698027</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1550114692153479</v>
+        <v>0.1544162681015729</v>
       </c>
       <c r="C46">
-        <v>216.2679206328048</v>
+        <v>215.608385314285</v>
       </c>
       <c r="D46">
-        <v>313.2319206328049</v>
+        <v>314.948385314285</v>
       </c>
       <c r="E46">
-        <v>-41.756</v>
+        <v>-39.38</v>
       </c>
       <c r="F46">
-        <v>104.544</v>
+        <v>106.92</v>
       </c>
       <c r="G46">
         <v>7.58</v>
@@ -5175,28 +5175,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M46">
-        <v>5.4153792</v>
+        <v>5.538456000000001</v>
       </c>
       <c r="N46">
-        <v>54.35128746666666</v>
+        <v>54.22821066666666</v>
       </c>
       <c r="O46">
-        <v>19.02295061333333</v>
+        <v>18.97987373333333</v>
       </c>
       <c r="P46">
-        <v>35.32833685333333</v>
+        <v>35.24833693333333</v>
       </c>
       <c r="Q46">
-        <v>60.72833685333333</v>
+        <v>60.64833693333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.250351195027407</v>
+        <v>0.253208669275587</v>
       </c>
       <c r="T46">
-        <v>1.005036152091302</v>
+        <v>1.019075986582154</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.0364693698027</v>
+        <v>10.7912144949182</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1544162681015729</v>
+        <v>0.1538210669877978</v>
       </c>
       <c r="C47">
-        <v>215.608385314285</v>
+        <v>214.9677655965583</v>
       </c>
       <c r="D47">
-        <v>314.948385314285</v>
+        <v>316.6837655965583</v>
       </c>
       <c r="E47">
-        <v>-39.38</v>
+        <v>-37.00399999999999</v>
       </c>
       <c r="F47">
-        <v>106.92</v>
+        <v>109.296</v>
       </c>
       <c r="G47">
         <v>7.58</v>
@@ -5257,28 +5257,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M47">
-        <v>5.538456000000001</v>
+        <v>5.661532800000001</v>
       </c>
       <c r="N47">
-        <v>54.22821066666666</v>
+        <v>54.10513386666666</v>
       </c>
       <c r="O47">
-        <v>18.97987373333333</v>
+        <v>18.93679685333333</v>
       </c>
       <c r="P47">
-        <v>35.24833693333333</v>
+        <v>35.16833701333333</v>
       </c>
       <c r="Q47">
-        <v>60.64833693333334</v>
+        <v>60.56833701333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.253208669275587</v>
+        <v>0.2561719759033292</v>
       </c>
       <c r="T47">
-        <v>1.019075986582154</v>
+        <v>1.033635814943038</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.7912144949182</v>
+        <v>10.55662287546345</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1538210669877978</v>
+        <v>0.1532258658740227</v>
       </c>
       <c r="C48">
-        <v>214.9677655965583</v>
+        <v>214.3463758895634</v>
       </c>
       <c r="D48">
-        <v>316.6837655965583</v>
+        <v>318.4383758895634</v>
       </c>
       <c r="E48">
-        <v>-37.00399999999999</v>
+        <v>-34.628</v>
       </c>
       <c r="F48">
-        <v>109.296</v>
+        <v>111.672</v>
       </c>
       <c r="G48">
         <v>7.58</v>
@@ -5339,28 +5339,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M48">
-        <v>5.661532800000001</v>
+        <v>5.7846096</v>
       </c>
       <c r="N48">
-        <v>54.10513386666666</v>
+        <v>53.98205706666666</v>
       </c>
       <c r="O48">
-        <v>18.93679685333333</v>
+        <v>18.89371997333333</v>
       </c>
       <c r="P48">
-        <v>35.16833701333333</v>
+        <v>35.08833709333334</v>
       </c>
       <c r="Q48">
-        <v>60.56833701333333</v>
+        <v>60.48833709333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2561719759033292</v>
+        <v>0.2592471054226843</v>
       </c>
       <c r="T48">
-        <v>1.033635814943038</v>
+        <v>1.048745070789238</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.55662287546345</v>
+        <v>10.33201387811317</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1532258658740227</v>
+        <v>0.1526306647602476</v>
       </c>
       <c r="C49">
-        <v>214.3463758895634</v>
+        <v>213.7445376101102</v>
       </c>
       <c r="D49">
-        <v>318.4383758895634</v>
+        <v>320.2125376101102</v>
       </c>
       <c r="E49">
-        <v>-34.628</v>
+        <v>-32.252</v>
       </c>
       <c r="F49">
-        <v>111.672</v>
+        <v>114.048</v>
       </c>
       <c r="G49">
         <v>7.58</v>
@@ -5421,28 +5421,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M49">
-        <v>5.7846096</v>
+        <v>5.907686400000001</v>
       </c>
       <c r="N49">
-        <v>53.98205706666666</v>
+        <v>53.85898026666666</v>
       </c>
       <c r="O49">
-        <v>18.89371997333333</v>
+        <v>18.85064309333333</v>
       </c>
       <c r="P49">
-        <v>35.08833709333334</v>
+        <v>35.00833717333333</v>
       </c>
       <c r="Q49">
-        <v>60.48833709333334</v>
+        <v>60.40833717333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2592471054226843</v>
+        <v>0.2624405091543223</v>
       </c>
       <c r="T49">
-        <v>1.048745070789238</v>
+        <v>1.064435451860292</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.33201387811317</v>
+        <v>10.11676358898581</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1526306647602476</v>
+        <v>0.1520354636464725</v>
       </c>
       <c r="C50">
-        <v>213.7445376101102</v>
+        <v>213.1625793781635</v>
       </c>
       <c r="D50">
-        <v>320.2125376101102</v>
+        <v>322.0065793781636</v>
       </c>
       <c r="E50">
-        <v>-32.25200000000001</v>
+        <v>-29.876</v>
       </c>
       <c r="F50">
-        <v>114.048</v>
+        <v>116.424</v>
       </c>
       <c r="G50">
         <v>7.58</v>
@@ -5503,28 +5503,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M50">
-        <v>5.9076864</v>
+        <v>6.0307632</v>
       </c>
       <c r="N50">
-        <v>53.85898026666666</v>
+        <v>53.73590346666666</v>
       </c>
       <c r="O50">
-        <v>18.85064309333333</v>
+        <v>18.80756621333333</v>
       </c>
       <c r="P50">
-        <v>35.00833717333333</v>
+        <v>34.92833725333333</v>
       </c>
       <c r="Q50">
-        <v>60.40833717333334</v>
+        <v>60.32833725333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2624405091543223</v>
+        <v>0.2657591444048481</v>
       </c>
       <c r="T50">
-        <v>1.064435451860292</v>
+        <v>1.080741141992955</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.11676358898581</v>
+        <v>9.910299025945283</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1520354636464725</v>
+        <v>0.1519927625326974</v>
       </c>
       <c r="C51">
-        <v>213.1625793781635</v>
+        <v>210.9160612680251</v>
       </c>
       <c r="D51">
-        <v>322.0065793781636</v>
+        <v>322.1360612680251</v>
       </c>
       <c r="E51">
-        <v>-29.876</v>
+        <v>-27.5</v>
       </c>
       <c r="F51">
-        <v>116.424</v>
+        <v>118.8</v>
       </c>
       <c r="G51">
         <v>7.58</v>
@@ -5585,45 +5585,45 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M51">
-        <v>6.0307632</v>
+        <v>6.3558</v>
       </c>
       <c r="N51">
-        <v>53.73590346666666</v>
+        <v>53.41086666666666</v>
       </c>
       <c r="O51">
-        <v>18.80756621333333</v>
+        <v>18.69380333333333</v>
       </c>
       <c r="P51">
-        <v>34.92833725333333</v>
+        <v>34.71706333333333</v>
       </c>
       <c r="Q51">
-        <v>60.32833725333333</v>
+        <v>60.11706333333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2657591444048481</v>
+        <v>0.2692105250653949</v>
       </c>
       <c r="T51">
-        <v>1.080741141992955</v>
+        <v>1.097699059730926</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.910299025945283</v>
+        <v>9.4034844813661</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1519927625326974</v>
+        <v>0.1514086114189224</v>
       </c>
       <c r="C52">
-        <v>210.9160612680251</v>
+        <v>210.3218869775819</v>
       </c>
       <c r="D52">
-        <v>322.1360612680251</v>
+        <v>323.9178869775819</v>
       </c>
       <c r="E52">
-        <v>-27.5</v>
+        <v>-25.124</v>
       </c>
       <c r="F52">
-        <v>118.8</v>
+        <v>121.176</v>
       </c>
       <c r="G52">
         <v>7.58</v>
@@ -5667,28 +5667,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M52">
-        <v>6.3558</v>
+        <v>6.482916</v>
       </c>
       <c r="N52">
-        <v>53.41086666666666</v>
+        <v>53.28375066666666</v>
       </c>
       <c r="O52">
-        <v>18.69380333333333</v>
+        <v>18.64931273333333</v>
       </c>
       <c r="P52">
-        <v>34.71706333333333</v>
+        <v>34.63443793333333</v>
       </c>
       <c r="Q52">
-        <v>60.11706333333333</v>
+        <v>60.03443793333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2692105250653949</v>
+        <v>0.272802778405964</v>
       </c>
       <c r="T52">
-        <v>1.097699059730926</v>
+        <v>1.115349137376568</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.4034844813661</v>
+        <v>9.219102432711862</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1514086114189224</v>
+        <v>0.1508244603051473</v>
       </c>
       <c r="C53">
-        <v>210.3218869775819</v>
+        <v>209.7475338882145</v>
       </c>
       <c r="D53">
-        <v>323.9178869775819</v>
+        <v>325.7195338882145</v>
       </c>
       <c r="E53">
-        <v>-25.124</v>
+        <v>-22.74799999999999</v>
       </c>
       <c r="F53">
-        <v>121.176</v>
+        <v>123.552</v>
       </c>
       <c r="G53">
         <v>7.58</v>
@@ -5749,28 +5749,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M53">
-        <v>6.482916</v>
+        <v>6.610032000000001</v>
       </c>
       <c r="N53">
-        <v>53.28375066666666</v>
+        <v>53.15663466666666</v>
       </c>
       <c r="O53">
-        <v>18.64931273333333</v>
+        <v>18.60482213333333</v>
       </c>
       <c r="P53">
-        <v>34.63443793333333</v>
+        <v>34.55181253333333</v>
       </c>
       <c r="Q53">
-        <v>60.03443793333334</v>
+        <v>59.95181253333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.272802778405964</v>
+        <v>0.2765447089690569</v>
       </c>
       <c r="T53">
-        <v>1.115349137376568</v>
+        <v>1.133734634924113</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.219102432711862</v>
+        <v>9.041812001313557</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1508244603051473</v>
+        <v>0.1502403091913722</v>
       </c>
       <c r="C54">
-        <v>209.7475338882145</v>
+        <v>209.1933345892299</v>
       </c>
       <c r="D54">
-        <v>325.7195338882145</v>
+        <v>327.5413345892299</v>
       </c>
       <c r="E54">
-        <v>-22.74799999999999</v>
+        <v>-20.372</v>
       </c>
       <c r="F54">
-        <v>123.552</v>
+        <v>125.928</v>
       </c>
       <c r="G54">
         <v>7.58</v>
@@ -5831,28 +5831,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M54">
-        <v>6.610032000000001</v>
+        <v>6.737148</v>
       </c>
       <c r="N54">
-        <v>53.15663466666666</v>
+        <v>53.02951866666667</v>
       </c>
       <c r="O54">
-        <v>18.60482213333333</v>
+        <v>18.56033153333333</v>
       </c>
       <c r="P54">
-        <v>34.55181253333333</v>
+        <v>34.46918713333334</v>
       </c>
       <c r="Q54">
-        <v>59.95181253333334</v>
+        <v>59.86918713333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2765447089690569</v>
+        <v>0.2804458706199409</v>
       </c>
       <c r="T54">
-        <v>1.133734634924113</v>
+        <v>1.152902494069425</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.041812001313557</v>
+        <v>8.871211774873681</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1502403091913722</v>
+        <v>0.1496561580775971</v>
       </c>
       <c r="C55">
-        <v>209.1933345892299</v>
+        <v>208.6596291526848</v>
       </c>
       <c r="D55">
-        <v>327.5413345892299</v>
+        <v>329.3836291526848</v>
       </c>
       <c r="E55">
-        <v>-20.372</v>
+        <v>-17.99599999999998</v>
       </c>
       <c r="F55">
-        <v>125.928</v>
+        <v>128.304</v>
       </c>
       <c r="G55">
         <v>7.58</v>
@@ -5913,28 +5913,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M55">
-        <v>6.737148</v>
+        <v>6.864264000000001</v>
       </c>
       <c r="N55">
-        <v>53.02951866666667</v>
+        <v>52.90240266666667</v>
       </c>
       <c r="O55">
-        <v>18.56033153333333</v>
+        <v>18.51584093333333</v>
       </c>
       <c r="P55">
-        <v>34.46918713333334</v>
+        <v>34.38656173333334</v>
       </c>
       <c r="Q55">
-        <v>59.86918713333334</v>
+        <v>59.78656173333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2804458706199409</v>
+        <v>0.2845166479947764</v>
       </c>
       <c r="T55">
-        <v>1.152902494069425</v>
+        <v>1.172903738394968</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.871211774873681</v>
+        <v>8.706930075338981</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1496561580775971</v>
+        <v>0.1490720069638221</v>
       </c>
       <c r="C56">
-        <v>208.6596291526848</v>
+        <v>208.1467653450144</v>
       </c>
       <c r="D56">
-        <v>329.3836291526848</v>
+        <v>331.2467653450144</v>
       </c>
       <c r="E56">
-        <v>-17.99599999999998</v>
+        <v>-15.61999999999998</v>
       </c>
       <c r="F56">
-        <v>128.304</v>
+        <v>130.68</v>
       </c>
       <c r="G56">
         <v>7.58</v>
@@ -5995,28 +5995,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M56">
-        <v>6.864264000000001</v>
+        <v>6.991380000000002</v>
       </c>
       <c r="N56">
-        <v>52.90240266666667</v>
+        <v>52.77528666666667</v>
       </c>
       <c r="O56">
-        <v>18.51584093333333</v>
+        <v>18.47135033333333</v>
       </c>
       <c r="P56">
-        <v>34.38656173333334</v>
+        <v>34.30393633333333</v>
       </c>
       <c r="Q56">
-        <v>59.78656173333334</v>
+        <v>59.70393633333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2845166479947764</v>
+        <v>0.2887683488084935</v>
       </c>
       <c r="T56">
-        <v>1.172903738394968</v>
+        <v>1.193793926912758</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.706930075338981</v>
+        <v>8.548622255787363</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1490720069638221</v>
+        <v>0.148487855850047</v>
       </c>
       <c r="C57">
-        <v>208.1467653450144</v>
+        <v>207.6550988458839</v>
       </c>
       <c r="D57">
-        <v>331.2467653450144</v>
+        <v>333.1310988458839</v>
       </c>
       <c r="E57">
-        <v>-15.61999999999998</v>
+        <v>-13.244</v>
       </c>
       <c r="F57">
-        <v>130.68</v>
+        <v>133.056</v>
       </c>
       <c r="G57">
         <v>7.58</v>
@@ -6077,28 +6077,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M57">
-        <v>6.991380000000002</v>
+        <v>7.118496</v>
       </c>
       <c r="N57">
-        <v>52.77528666666667</v>
+        <v>52.64817066666667</v>
       </c>
       <c r="O57">
-        <v>18.47135033333333</v>
+        <v>18.42685973333333</v>
       </c>
       <c r="P57">
-        <v>34.30393633333333</v>
+        <v>34.22131093333333</v>
       </c>
       <c r="Q57">
-        <v>59.70393633333333</v>
+        <v>59.62131093333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2887683488084935</v>
+        <v>0.2932133087501068</v>
       </c>
       <c r="T57">
-        <v>1.193793926912758</v>
+        <v>1.215633669454083</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.548622255787363</v>
+        <v>8.395968286934018</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.148487855850047</v>
+        <v>0.1479037047362719</v>
       </c>
       <c r="C58">
-        <v>207.6550988458839</v>
+        <v>207.1849934745516</v>
       </c>
       <c r="D58">
-        <v>333.1310988458839</v>
+        <v>335.0369934745517</v>
       </c>
       <c r="E58">
-        <v>-13.244</v>
+        <v>-10.86799999999999</v>
       </c>
       <c r="F58">
-        <v>133.056</v>
+        <v>135.432</v>
       </c>
       <c r="G58">
         <v>7.58</v>
@@ -6159,28 +6159,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M58">
-        <v>7.118496</v>
+        <v>7.245612</v>
       </c>
       <c r="N58">
-        <v>52.64817066666667</v>
+        <v>52.52105466666666</v>
       </c>
       <c r="O58">
-        <v>18.42685973333333</v>
+        <v>18.38236913333333</v>
       </c>
       <c r="P58">
-        <v>34.22131093333333</v>
+        <v>34.13868553333333</v>
       </c>
       <c r="Q58">
-        <v>59.62131093333333</v>
+        <v>59.53868553333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2932133087501068</v>
+        <v>0.2978650110145858</v>
       </c>
       <c r="T58">
-        <v>1.215633669454083</v>
+        <v>1.238489213974075</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.395968286934018</v>
+        <v>8.248670597689561</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1479037047362719</v>
+        <v>0.1473195536224968</v>
       </c>
       <c r="C59">
-        <v>207.1849934745516</v>
+        <v>206.7368214240496</v>
       </c>
       <c r="D59">
-        <v>335.0369934745517</v>
+        <v>336.9648214240496</v>
       </c>
       <c r="E59">
-        <v>-10.86799999999999</v>
+        <v>-8.49199999999999</v>
       </c>
       <c r="F59">
-        <v>135.432</v>
+        <v>137.808</v>
       </c>
       <c r="G59">
         <v>7.58</v>
@@ -6241,28 +6241,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M59">
-        <v>7.245612</v>
+        <v>7.372728000000001</v>
       </c>
       <c r="N59">
-        <v>52.52105466666666</v>
+        <v>52.39393866666666</v>
       </c>
       <c r="O59">
-        <v>18.38236913333333</v>
+        <v>18.33787853333333</v>
       </c>
       <c r="P59">
-        <v>34.13868553333333</v>
+        <v>34.05606013333333</v>
       </c>
       <c r="Q59">
-        <v>59.53868553333334</v>
+        <v>59.45606013333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2978650110145858</v>
+        <v>0.3027382229107067</v>
       </c>
       <c r="T59">
-        <v>1.238489213974075</v>
+        <v>1.262433117756923</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.248670597689561</v>
+        <v>8.106452139108708</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1473195536224968</v>
+        <v>0.1467354025087217</v>
       </c>
       <c r="C60">
-        <v>206.7368214240496</v>
+        <v>206.3109635034936</v>
       </c>
       <c r="D60">
-        <v>336.9648214240496</v>
+        <v>338.9149635034937</v>
       </c>
       <c r="E60">
-        <v>-8.492000000000019</v>
+        <v>-6.116000000000014</v>
       </c>
       <c r="F60">
-        <v>137.808</v>
+        <v>140.184</v>
       </c>
       <c r="G60">
         <v>7.58</v>
@@ -6323,28 +6323,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M60">
-        <v>7.372728</v>
+        <v>7.499844</v>
       </c>
       <c r="N60">
-        <v>52.39393866666666</v>
+        <v>52.26682266666667</v>
       </c>
       <c r="O60">
-        <v>18.33787853333333</v>
+        <v>18.29338793333333</v>
       </c>
       <c r="P60">
-        <v>34.05606013333333</v>
+        <v>33.97343473333333</v>
       </c>
       <c r="Q60">
-        <v>59.45606013333334</v>
+        <v>59.37343473333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3027382229107067</v>
+        <v>0.3078491524602969</v>
       </c>
       <c r="T60">
-        <v>1.262433117756923</v>
+        <v>1.287545016846252</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.106452139108708</v>
+        <v>7.96905464522551</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1467354025087217</v>
+        <v>0.1461512513949466</v>
       </c>
       <c r="C61">
-        <v>206.3109635034936</v>
+        <v>205.9078093888573</v>
       </c>
       <c r="D61">
-        <v>338.9149635034937</v>
+        <v>340.8878093888573</v>
       </c>
       <c r="E61">
-        <v>-6.116000000000014</v>
+        <v>-3.740000000000009</v>
       </c>
       <c r="F61">
-        <v>140.184</v>
+        <v>142.56</v>
       </c>
       <c r="G61">
         <v>7.58</v>
@@ -6405,28 +6405,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M61">
-        <v>7.499844</v>
+        <v>7.62696</v>
       </c>
       <c r="N61">
-        <v>52.26682266666667</v>
+        <v>52.13970666666667</v>
       </c>
       <c r="O61">
-        <v>18.29338793333333</v>
+        <v>18.24889733333333</v>
       </c>
       <c r="P61">
-        <v>33.97343473333333</v>
+        <v>33.89080933333334</v>
       </c>
       <c r="Q61">
-        <v>59.37343473333334</v>
+        <v>59.29080933333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3078491524602969</v>
+        <v>0.3132156284873666</v>
       </c>
       <c r="T61">
-        <v>1.287545016846252</v>
+        <v>1.313912510890047</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.96905464522551</v>
+        <v>7.836237067805085</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1461512513949466</v>
+        <v>0.1455671002811716</v>
       </c>
       <c r="C62">
-        <v>205.9078093888573</v>
+        <v>205.5277578825555</v>
       </c>
       <c r="D62">
-        <v>340.8878093888573</v>
+        <v>342.8837578825555</v>
       </c>
       <c r="E62">
-        <v>-3.740000000000009</v>
+        <v>-1.364000000000004</v>
       </c>
       <c r="F62">
-        <v>142.56</v>
+        <v>144.936</v>
       </c>
       <c r="G62">
         <v>7.58</v>
@@ -6487,28 +6487,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M62">
-        <v>7.62696</v>
+        <v>7.754076</v>
       </c>
       <c r="N62">
-        <v>52.13970666666667</v>
+        <v>52.01259066666667</v>
       </c>
       <c r="O62">
-        <v>18.24889733333333</v>
+        <v>18.20440673333333</v>
       </c>
       <c r="P62">
-        <v>33.89080933333334</v>
+        <v>33.80818393333334</v>
       </c>
       <c r="Q62">
-        <v>59.29080933333334</v>
+        <v>59.20818393333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3132156284873666</v>
+        <v>0.3188573084132604</v>
       </c>
       <c r="T62">
-        <v>1.313912510890047</v>
+        <v>1.341632184115576</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.836237067805085</v>
+        <v>7.707774165054182</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1455671002811716</v>
+        <v>0.1453053491673965</v>
       </c>
       <c r="C63">
-        <v>205.5277578825555</v>
+        <v>204.0537215083517</v>
       </c>
       <c r="D63">
-        <v>342.8837578825555</v>
+        <v>343.7857215083517</v>
       </c>
       <c r="E63">
-        <v>-1.364000000000004</v>
+        <v>1.012</v>
       </c>
       <c r="F63">
-        <v>144.936</v>
+        <v>147.312</v>
       </c>
       <c r="G63">
         <v>7.58</v>
@@ -6569,45 +6569,45 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M63">
-        <v>7.754076</v>
+        <v>7.999041600000001</v>
       </c>
       <c r="N63">
-        <v>52.01259066666667</v>
+        <v>51.76762506666667</v>
       </c>
       <c r="O63">
-        <v>18.20440673333333</v>
+        <v>18.11866877333333</v>
       </c>
       <c r="P63">
-        <v>33.80818393333334</v>
+        <v>33.64895629333333</v>
       </c>
       <c r="Q63">
-        <v>59.20818393333334</v>
+        <v>59.04895629333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3188573084132604</v>
+        <v>0.3247959188615697</v>
       </c>
       <c r="T63">
-        <v>1.341632184115576</v>
+        <v>1.370810787510869</v>
       </c>
       <c r="U63">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>7.707774165054182</v>
+        <v>7.471728446401212</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1453053491673965</v>
+        <v>0.1447263980536214</v>
       </c>
       <c r="C64">
-        <v>204.0537215083517</v>
+        <v>203.6896731237268</v>
       </c>
       <c r="D64">
-        <v>343.7857215083517</v>
+        <v>345.7976731237268</v>
       </c>
       <c r="E64">
-        <v>1.012</v>
+        <v>3.388000000000005</v>
       </c>
       <c r="F64">
-        <v>147.312</v>
+        <v>149.688</v>
       </c>
       <c r="G64">
         <v>7.58</v>
@@ -6651,28 +6651,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M64">
-        <v>7.999041600000001</v>
+        <v>8.1280584</v>
       </c>
       <c r="N64">
-        <v>51.76762506666667</v>
+        <v>51.63860826666667</v>
       </c>
       <c r="O64">
-        <v>18.11866877333333</v>
+        <v>18.07351289333333</v>
       </c>
       <c r="P64">
-        <v>33.64895629333333</v>
+        <v>33.56509537333334</v>
       </c>
       <c r="Q64">
-        <v>59.04895629333333</v>
+        <v>58.96509537333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3247959188615697</v>
+        <v>0.3310555352800579</v>
       </c>
       <c r="T64">
-        <v>1.370810787510869</v>
+        <v>1.401566612711313</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.471728446401212</v>
+        <v>7.353129582172621</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1447263980536214</v>
+        <v>0.1441474469398463</v>
       </c>
       <c r="C65">
-        <v>203.6896731237268</v>
+        <v>203.3493126265831</v>
       </c>
       <c r="D65">
-        <v>345.7976731237268</v>
+        <v>347.8333126265832</v>
       </c>
       <c r="E65">
-        <v>3.388000000000005</v>
+        <v>5.76400000000001</v>
       </c>
       <c r="F65">
-        <v>149.688</v>
+        <v>152.064</v>
       </c>
       <c r="G65">
         <v>7.58</v>
@@ -6733,28 +6733,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M65">
-        <v>8.1280584</v>
+        <v>8.257075200000001</v>
       </c>
       <c r="N65">
-        <v>51.63860826666667</v>
+        <v>51.50959146666666</v>
       </c>
       <c r="O65">
-        <v>18.07351289333333</v>
+        <v>18.02835701333333</v>
       </c>
       <c r="P65">
-        <v>33.56509537333334</v>
+        <v>33.48123445333333</v>
       </c>
       <c r="Q65">
-        <v>58.96509537333334</v>
+        <v>58.88123445333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3310555352800579</v>
+        <v>0.3376629081662398</v>
       </c>
       <c r="T65">
-        <v>1.401566612711313</v>
+        <v>1.434031094867337</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.353129582172621</v>
+        <v>7.238236932451173</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1441474469398463</v>
+        <v>0.1435684958260713</v>
       </c>
       <c r="C66">
-        <v>203.3493126265831</v>
+        <v>203.0330608312756</v>
       </c>
       <c r="D66">
-        <v>347.8333126265832</v>
+        <v>349.8930608312756</v>
       </c>
       <c r="E66">
-        <v>5.76400000000001</v>
+        <v>8.140000000000015</v>
       </c>
       <c r="F66">
-        <v>152.064</v>
+        <v>154.44</v>
       </c>
       <c r="G66">
         <v>7.58</v>
@@ -6815,28 +6815,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M66">
-        <v>8.257075200000001</v>
+        <v>8.386092000000001</v>
       </c>
       <c r="N66">
-        <v>51.50959146666666</v>
+        <v>51.38057466666666</v>
       </c>
       <c r="O66">
-        <v>18.02835701333333</v>
+        <v>17.98320113333333</v>
       </c>
       <c r="P66">
-        <v>33.48123445333333</v>
+        <v>33.39737353333333</v>
       </c>
       <c r="Q66">
-        <v>58.88123445333333</v>
+        <v>58.79737353333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3376629081662398</v>
+        <v>0.3446478452173464</v>
       </c>
       <c r="T66">
-        <v>1.434031094867337</v>
+        <v>1.46835069028942</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.238236932451173</v>
+        <v>7.126879441182693</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1435684958260713</v>
+        <v>0.1429895447122961</v>
       </c>
       <c r="C67">
-        <v>203.0330608312756</v>
+        <v>202.7413485792027</v>
       </c>
       <c r="D67">
-        <v>349.8930608312756</v>
+        <v>351.9773485792028</v>
       </c>
       <c r="E67">
-        <v>8.140000000000015</v>
+        <v>10.51600000000002</v>
       </c>
       <c r="F67">
-        <v>154.44</v>
+        <v>156.816</v>
       </c>
       <c r="G67">
         <v>7.58</v>
@@ -6897,28 +6897,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M67">
-        <v>8.386092000000001</v>
+        <v>8.515108800000002</v>
       </c>
       <c r="N67">
-        <v>51.38057466666666</v>
+        <v>51.25155786666667</v>
       </c>
       <c r="O67">
-        <v>17.98320113333333</v>
+        <v>17.93804525333333</v>
       </c>
       <c r="P67">
-        <v>33.39737353333333</v>
+        <v>33.31351261333333</v>
       </c>
       <c r="Q67">
-        <v>58.79737353333333</v>
+        <v>58.71351261333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3446478452173464</v>
+        <v>0.3520436609185181</v>
       </c>
       <c r="T67">
-        <v>1.46835069028942</v>
+        <v>1.504689085442213</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.126879441182693</v>
+        <v>7.018896419346592</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1429895447122961</v>
+        <v>0.1424105935985211</v>
       </c>
       <c r="C68">
-        <v>202.7413485792027</v>
+        <v>202.474617039247</v>
       </c>
       <c r="D68">
-        <v>351.9773485792028</v>
+        <v>354.086617039247</v>
       </c>
       <c r="E68">
-        <v>10.51600000000002</v>
+        <v>12.89200000000002</v>
       </c>
       <c r="F68">
-        <v>156.816</v>
+        <v>159.192</v>
       </c>
       <c r="G68">
         <v>7.58</v>
@@ -6979,28 +6979,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M68">
-        <v>8.515108800000002</v>
+        <v>8.644125600000002</v>
       </c>
       <c r="N68">
-        <v>51.25155786666667</v>
+        <v>51.12254106666666</v>
       </c>
       <c r="O68">
-        <v>17.93804525333333</v>
+        <v>17.89288937333333</v>
       </c>
       <c r="P68">
-        <v>33.31351261333333</v>
+        <v>33.22965169333333</v>
       </c>
       <c r="Q68">
-        <v>58.71351261333334</v>
+        <v>58.62965169333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3520436609185181</v>
+        <v>0.3598877078743064</v>
       </c>
       <c r="T68">
-        <v>1.504689085442213</v>
+        <v>1.543229807573965</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.018896419346592</v>
+        <v>6.914136771296642</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1424105935985211</v>
+        <v>0.141831642484746</v>
       </c>
       <c r="C69">
-        <v>202.474617039247</v>
+        <v>202.2333180190859</v>
       </c>
       <c r="D69">
-        <v>354.086617039247</v>
+        <v>356.2213180190859</v>
       </c>
       <c r="E69">
-        <v>12.89200000000002</v>
+        <v>15.26800000000003</v>
       </c>
       <c r="F69">
-        <v>159.192</v>
+        <v>161.568</v>
       </c>
       <c r="G69">
         <v>7.58</v>
@@ -7061,28 +7061,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M69">
-        <v>8.644125600000002</v>
+        <v>8.773142400000003</v>
       </c>
       <c r="N69">
-        <v>51.12254106666666</v>
+        <v>50.99352426666666</v>
       </c>
       <c r="O69">
-        <v>17.89288937333333</v>
+        <v>17.84773349333333</v>
       </c>
       <c r="P69">
-        <v>33.22965169333333</v>
+        <v>33.14579077333333</v>
       </c>
       <c r="Q69">
-        <v>58.62965169333333</v>
+        <v>58.54579077333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3598877078743064</v>
+        <v>0.3682220077648313</v>
       </c>
       <c r="T69">
-        <v>1.543229807573965</v>
+        <v>1.58417932483895</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.914136771296642</v>
+        <v>6.812458289365809</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.141831642484746</v>
+        <v>0.1412526913709709</v>
       </c>
       <c r="C70">
-        <v>202.2333180190859</v>
+        <v>202.0179142878288</v>
       </c>
       <c r="D70">
-        <v>356.2213180190859</v>
+        <v>358.3819142878288</v>
       </c>
       <c r="E70">
-        <v>15.26800000000003</v>
+        <v>17.64400000000001</v>
       </c>
       <c r="F70">
-        <v>161.568</v>
+        <v>163.944</v>
       </c>
       <c r="G70">
         <v>7.58</v>
@@ -7143,28 +7143,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M70">
-        <v>8.773142400000003</v>
+        <v>8.902159200000002</v>
       </c>
       <c r="N70">
-        <v>50.99352426666666</v>
+        <v>50.86450746666667</v>
       </c>
       <c r="O70">
-        <v>17.84773349333333</v>
+        <v>17.80257761333333</v>
       </c>
       <c r="P70">
-        <v>33.14579077333333</v>
+        <v>33.06192985333334</v>
       </c>
       <c r="Q70">
-        <v>58.54579077333334</v>
+        <v>58.46192985333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3682220077648313</v>
+        <v>0.3770940044224869</v>
       </c>
       <c r="T70">
-        <v>1.58417932483895</v>
+        <v>1.627770746443611</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.812458289365809</v>
+        <v>6.713727009809784</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1412526913709709</v>
+        <v>0.1406737402571958</v>
       </c>
       <c r="C71">
-        <v>202.0179142878288</v>
+        <v>201.8288799104688</v>
       </c>
       <c r="D71">
-        <v>358.3819142878288</v>
+        <v>360.5688799104689</v>
       </c>
       <c r="E71">
-        <v>17.64400000000001</v>
+        <v>20.02000000000001</v>
       </c>
       <c r="F71">
-        <v>163.944</v>
+        <v>166.32</v>
       </c>
       <c r="G71">
         <v>7.58</v>
@@ -7225,28 +7225,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M71">
-        <v>8.902159200000002</v>
+        <v>9.031176000000002</v>
       </c>
       <c r="N71">
-        <v>50.86450746666667</v>
+        <v>50.73549066666666</v>
       </c>
       <c r="O71">
-        <v>17.80257761333333</v>
+        <v>17.75742173333333</v>
       </c>
       <c r="P71">
-        <v>33.06192985333334</v>
+        <v>32.97806893333333</v>
       </c>
       <c r="Q71">
-        <v>58.46192985333334</v>
+        <v>58.37806893333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3770940044224869</v>
+        <v>0.3865574675239862</v>
       </c>
       <c r="T71">
-        <v>1.627770746443611</v>
+        <v>1.674268262821917</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.713727009809784</v>
+        <v>6.617816623955358</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1406737402571958</v>
+        <v>0.1400947891434208</v>
       </c>
       <c r="C72">
-        <v>201.8288799104688</v>
+        <v>201.6667005946563</v>
       </c>
       <c r="D72">
-        <v>360.5688799104689</v>
+        <v>362.7827005946564</v>
       </c>
       <c r="E72">
-        <v>20.02000000000001</v>
+        <v>22.39600000000002</v>
       </c>
       <c r="F72">
-        <v>166.32</v>
+        <v>168.696</v>
       </c>
       <c r="G72">
         <v>7.58</v>
@@ -7307,28 +7307,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M72">
-        <v>9.031176000000002</v>
+        <v>9.160192800000001</v>
       </c>
       <c r="N72">
-        <v>50.73549066666666</v>
+        <v>50.60647386666666</v>
       </c>
       <c r="O72">
-        <v>17.75742173333333</v>
+        <v>17.71226585333333</v>
       </c>
       <c r="P72">
-        <v>32.97806893333333</v>
+        <v>32.89420801333333</v>
       </c>
       <c r="Q72">
-        <v>58.37806893333334</v>
+        <v>58.29420801333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3865574675239862</v>
+        <v>0.3966735832531752</v>
       </c>
       <c r="T72">
-        <v>1.674268262821917</v>
+        <v>1.723972504467693</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.617816623955358</v>
+        <v>6.524607939110917</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1400947891434208</v>
+        <v>0.1395158380296457</v>
       </c>
       <c r="C73">
-        <v>201.6667005946564</v>
+        <v>201.5318740503232</v>
       </c>
       <c r="D73">
-        <v>362.7827005946564</v>
+        <v>365.0238740503232</v>
       </c>
       <c r="E73">
-        <v>22.39599999999999</v>
+        <v>24.77199999999999</v>
       </c>
       <c r="F73">
-        <v>168.696</v>
+        <v>171.072</v>
       </c>
       <c r="G73">
         <v>7.58</v>
@@ -7389,28 +7389,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M73">
-        <v>9.160192800000001</v>
+        <v>9.2892096</v>
       </c>
       <c r="N73">
-        <v>50.60647386666666</v>
+        <v>50.47745706666667</v>
       </c>
       <c r="O73">
-        <v>17.71226585333333</v>
+        <v>17.66710997333333</v>
       </c>
       <c r="P73">
-        <v>32.89420801333333</v>
+        <v>32.81034709333333</v>
       </c>
       <c r="Q73">
-        <v>58.29420801333333</v>
+        <v>58.21034709333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.396673583253175</v>
+        <v>0.407512278677306</v>
       </c>
       <c r="T73">
-        <v>1.723972504467692</v>
+        <v>1.777227049088165</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.524607939110917</v>
+        <v>6.433988384401044</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1395158380296457</v>
+        <v>0.1389368869158706</v>
       </c>
       <c r="C74">
-        <v>201.5318740503232</v>
+        <v>201.4249103627223</v>
       </c>
       <c r="D74">
-        <v>365.0238740503232</v>
+        <v>367.2929103627223</v>
       </c>
       <c r="E74">
-        <v>24.77199999999999</v>
+        <v>27.148</v>
       </c>
       <c r="F74">
-        <v>171.072</v>
+        <v>173.448</v>
       </c>
       <c r="G74">
         <v>7.58</v>
@@ -7471,28 +7471,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M74">
-        <v>9.2892096</v>
+        <v>9.4182264</v>
       </c>
       <c r="N74">
-        <v>50.47745706666667</v>
+        <v>50.34844026666666</v>
       </c>
       <c r="O74">
-        <v>17.66710997333333</v>
+        <v>17.62195409333333</v>
       </c>
       <c r="P74">
-        <v>32.81034709333333</v>
+        <v>32.72648617333333</v>
       </c>
       <c r="Q74">
-        <v>58.21034709333334</v>
+        <v>58.12648617333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.407512278677306</v>
+        <v>0.4191538404291504</v>
       </c>
       <c r="T74">
-        <v>1.777227049088165</v>
+        <v>1.834426374791637</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.433988384401044</v>
+        <v>6.345851557217467</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1389368869158706</v>
+        <v>0.1383579358020955</v>
       </c>
       <c r="C75">
-        <v>201.4249103627223</v>
+        <v>201.3463323794672</v>
       </c>
       <c r="D75">
-        <v>367.2929103627223</v>
+        <v>369.5903323794672</v>
       </c>
       <c r="E75">
-        <v>27.148</v>
+        <v>29.524</v>
       </c>
       <c r="F75">
-        <v>173.448</v>
+        <v>175.824</v>
       </c>
       <c r="G75">
         <v>7.58</v>
@@ -7553,28 +7553,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M75">
-        <v>9.4182264</v>
+        <v>9.5472432</v>
       </c>
       <c r="N75">
-        <v>50.34844026666666</v>
+        <v>50.21942346666667</v>
       </c>
       <c r="O75">
-        <v>17.62195409333333</v>
+        <v>17.57679821333333</v>
       </c>
       <c r="P75">
-        <v>32.72648617333333</v>
+        <v>32.64262525333334</v>
       </c>
       <c r="Q75">
-        <v>58.12648617333333</v>
+        <v>58.04262525333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4191538404291504</v>
+        <v>0.4316909069311366</v>
       </c>
       <c r="T75">
-        <v>1.834426374791637</v>
+        <v>1.896025648626144</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.345851557217467</v>
+        <v>6.260096806444259</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1383579358020955</v>
+        <v>0.1377789846883204</v>
       </c>
       <c r="C76">
-        <v>201.3463323794672</v>
+        <v>201.2966761121868</v>
       </c>
       <c r="D76">
-        <v>369.5903323794672</v>
+        <v>371.9166761121868</v>
       </c>
       <c r="E76">
-        <v>29.524</v>
+        <v>31.90000000000001</v>
       </c>
       <c r="F76">
-        <v>175.824</v>
+        <v>178.2</v>
       </c>
       <c r="G76">
         <v>7.58</v>
@@ -7635,28 +7635,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M76">
-        <v>9.5472432</v>
+        <v>9.676260000000001</v>
       </c>
       <c r="N76">
-        <v>50.21942346666667</v>
+        <v>50.09040666666667</v>
       </c>
       <c r="O76">
-        <v>17.57679821333333</v>
+        <v>17.53164233333333</v>
       </c>
       <c r="P76">
-        <v>32.64262525333334</v>
+        <v>32.55876433333334</v>
       </c>
       <c r="Q76">
-        <v>58.04262525333334</v>
+        <v>57.95876433333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4316909069311366</v>
+        <v>0.4452309387532818</v>
       </c>
       <c r="T76">
-        <v>1.896025648626144</v>
+        <v>1.962552864367413</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.260096806444259</v>
+        <v>6.176628849025001</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1377789846883204</v>
+        <v>0.1376940335745454</v>
       </c>
       <c r="C77">
-        <v>201.2966761121868</v>
+        <v>199.2644931657893</v>
       </c>
       <c r="D77">
-        <v>371.9166761121868</v>
+        <v>372.2604931657893</v>
       </c>
       <c r="E77">
-        <v>31.90000000000001</v>
+        <v>34.27600000000001</v>
       </c>
       <c r="F77">
-        <v>178.2</v>
+        <v>180.576</v>
       </c>
       <c r="G77">
         <v>7.58</v>
@@ -7717,45 +7717,45 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M77">
-        <v>9.676260000000001</v>
+        <v>9.985852800000002</v>
       </c>
       <c r="N77">
-        <v>50.09040666666667</v>
+        <v>49.78081386666666</v>
       </c>
       <c r="O77">
-        <v>17.53164233333333</v>
+        <v>17.42328485333333</v>
       </c>
       <c r="P77">
-        <v>32.55876433333334</v>
+        <v>32.35752901333333</v>
       </c>
       <c r="Q77">
-        <v>57.95876433333333</v>
+        <v>57.75752901333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4452309387532818</v>
+        <v>0.4598993065606057</v>
       </c>
       <c r="T77">
-        <v>1.962552864367413</v>
+        <v>2.034624014753787</v>
       </c>
       <c r="U77">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>6.176628849025001</v>
+        <v>5.985133955376015</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1376940335745454</v>
+        <v>0.1371215824607703</v>
       </c>
       <c r="C78">
-        <v>199.2644931657893</v>
+        <v>199.2220152991664</v>
       </c>
       <c r="D78">
-        <v>372.2604931657893</v>
+        <v>374.5940152991664</v>
       </c>
       <c r="E78">
-        <v>34.27600000000001</v>
+        <v>36.65200000000002</v>
       </c>
       <c r="F78">
-        <v>180.576</v>
+        <v>182.952</v>
       </c>
       <c r="G78">
         <v>7.58</v>
@@ -7799,28 +7799,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M78">
-        <v>9.985852800000002</v>
+        <v>10.1172456</v>
       </c>
       <c r="N78">
-        <v>49.78081386666666</v>
+        <v>49.64942106666666</v>
       </c>
       <c r="O78">
-        <v>17.42328485333333</v>
+        <v>17.37729737333333</v>
       </c>
       <c r="P78">
-        <v>32.35752901333333</v>
+        <v>32.27212369333333</v>
       </c>
       <c r="Q78">
-        <v>57.75752901333334</v>
+        <v>57.67212369333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4598993065606057</v>
+        <v>0.4758431846120447</v>
       </c>
       <c r="T78">
-        <v>2.034624014753787</v>
+        <v>2.112962221695497</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.985133955376015</v>
+        <v>5.907404942968534</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1371215824607703</v>
+        <v>0.1365491313469952</v>
       </c>
       <c r="C79">
-        <v>199.2220152991664</v>
+        <v>199.2089774354269</v>
       </c>
       <c r="D79">
-        <v>374.5940152991664</v>
+        <v>376.9569774354269</v>
       </c>
       <c r="E79">
-        <v>36.65200000000002</v>
+        <v>39.02800000000002</v>
       </c>
       <c r="F79">
-        <v>182.952</v>
+        <v>185.328</v>
       </c>
       <c r="G79">
         <v>7.58</v>
@@ -7881,28 +7881,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M79">
-        <v>10.1172456</v>
+        <v>10.2486384</v>
       </c>
       <c r="N79">
-        <v>49.64942106666666</v>
+        <v>49.51802826666666</v>
       </c>
       <c r="O79">
-        <v>17.37729737333333</v>
+        <v>17.33130989333333</v>
       </c>
       <c r="P79">
-        <v>32.27212369333333</v>
+        <v>32.18671837333333</v>
       </c>
       <c r="Q79">
-        <v>57.67212369333333</v>
+        <v>57.58671837333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4758431846120447</v>
+        <v>0.4932365061227055</v>
       </c>
       <c r="T79">
-        <v>2.112962221695497</v>
+        <v>2.198422083813727</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.907404942968534</v>
+        <v>5.831668982161244</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1365491313469952</v>
+        <v>0.1359766802332201</v>
       </c>
       <c r="C80">
-        <v>199.2089774354269</v>
+        <v>199.2259402393371</v>
       </c>
       <c r="D80">
-        <v>376.9569774354269</v>
+        <v>379.3499402393371</v>
       </c>
       <c r="E80">
-        <v>39.02800000000002</v>
+        <v>41.40400000000002</v>
       </c>
       <c r="F80">
-        <v>185.328</v>
+        <v>187.704</v>
       </c>
       <c r="G80">
         <v>7.58</v>
@@ -7963,28 +7963,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M80">
-        <v>10.2486384</v>
+        <v>10.3800312</v>
       </c>
       <c r="N80">
-        <v>49.51802826666666</v>
+        <v>49.38663546666666</v>
       </c>
       <c r="O80">
-        <v>17.33130989333333</v>
+        <v>17.28532241333333</v>
       </c>
       <c r="P80">
-        <v>32.18671837333333</v>
+        <v>32.10131305333333</v>
       </c>
       <c r="Q80">
-        <v>57.58671837333334</v>
+        <v>57.50131305333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4932365061227055</v>
+        <v>0.5122863344439054</v>
       </c>
       <c r="T80">
-        <v>2.198422083813727</v>
+        <v>2.292020980419408</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.831668982161244</v>
+        <v>5.757850387450342</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1359766802332201</v>
+        <v>0.135404229119445</v>
       </c>
       <c r="C81">
-        <v>199.2259402393371</v>
+        <v>199.2734787032531</v>
       </c>
       <c r="D81">
-        <v>379.3499402393371</v>
+        <v>381.7734787032532</v>
       </c>
       <c r="E81">
-        <v>41.40400000000002</v>
+        <v>43.78000000000003</v>
       </c>
       <c r="F81">
-        <v>187.704</v>
+        <v>190.08</v>
       </c>
       <c r="G81">
         <v>7.58</v>
@@ -8045,28 +8045,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M81">
-        <v>10.3800312</v>
+        <v>10.511424</v>
       </c>
       <c r="N81">
-        <v>49.38663546666666</v>
+        <v>49.25524266666666</v>
       </c>
       <c r="O81">
-        <v>17.28532241333333</v>
+        <v>17.23933493333333</v>
       </c>
       <c r="P81">
-        <v>32.10131305333333</v>
+        <v>32.01590773333334</v>
       </c>
       <c r="Q81">
-        <v>57.50131305333333</v>
+        <v>57.41590773333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5122863344439054</v>
+        <v>0.5332411455972252</v>
       </c>
       <c r="T81">
-        <v>2.292020980419408</v>
+        <v>2.394979766685656</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.757850387450342</v>
+        <v>5.685877257607213</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.135404229119445</v>
+        <v>0.1348317780056699</v>
       </c>
       <c r="C82">
-        <v>199.2734787032531</v>
+        <v>199.3521826077348</v>
       </c>
       <c r="D82">
-        <v>381.7734787032532</v>
+        <v>384.2281826077349</v>
       </c>
       <c r="E82">
-        <v>43.78000000000003</v>
+        <v>46.15600000000001</v>
       </c>
       <c r="F82">
-        <v>190.08</v>
+        <v>192.456</v>
       </c>
       <c r="G82">
         <v>7.58</v>
@@ -8127,28 +8127,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M82">
-        <v>10.511424</v>
+        <v>10.6428168</v>
       </c>
       <c r="N82">
-        <v>49.25524266666666</v>
+        <v>49.12384986666666</v>
       </c>
       <c r="O82">
-        <v>17.23933493333333</v>
+        <v>17.19334745333333</v>
       </c>
       <c r="P82">
-        <v>32.01590773333334</v>
+        <v>31.93050241333333</v>
       </c>
       <c r="Q82">
-        <v>57.41590773333334</v>
+        <v>57.33050241333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5332411455972252</v>
+        <v>0.5564017263456315</v>
       </c>
       <c r="T82">
-        <v>2.394979766685656</v>
+        <v>2.508776319927299</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.685877257607213</v>
+        <v>5.615681242081199</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1348317780056699</v>
+        <v>0.1342593268918948</v>
       </c>
       <c r="C83">
-        <v>199.3521826077348</v>
+        <v>199.4626570000437</v>
       </c>
       <c r="D83">
-        <v>384.2281826077349</v>
+        <v>386.7146570000438</v>
       </c>
       <c r="E83">
-        <v>46.15600000000001</v>
+        <v>48.53200000000001</v>
       </c>
       <c r="F83">
-        <v>192.456</v>
+        <v>194.832</v>
       </c>
       <c r="G83">
         <v>7.58</v>
@@ -8209,28 +8209,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M83">
-        <v>10.6428168</v>
+        <v>10.7742096</v>
       </c>
       <c r="N83">
-        <v>49.12384986666666</v>
+        <v>48.99245706666667</v>
       </c>
       <c r="O83">
-        <v>17.19334745333333</v>
+        <v>17.14735997333333</v>
       </c>
       <c r="P83">
-        <v>31.93050241333333</v>
+        <v>31.84509709333333</v>
       </c>
       <c r="Q83">
-        <v>57.33050241333333</v>
+        <v>57.24509709333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5564017263456315</v>
+        <v>0.5821357049549716</v>
       </c>
       <c r="T83">
-        <v>2.508776319927299</v>
+        <v>2.635216934640236</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.615681242081199</v>
+        <v>5.547197324494844</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1342593268918948</v>
+        <v>0.1336868757781198</v>
       </c>
       <c r="C84">
-        <v>199.4626570000437</v>
+        <v>199.605522691341</v>
       </c>
       <c r="D84">
-        <v>386.7146570000438</v>
+        <v>389.233522691341</v>
       </c>
       <c r="E84">
-        <v>48.53200000000001</v>
+        <v>50.90800000000002</v>
       </c>
       <c r="F84">
-        <v>194.832</v>
+        <v>197.208</v>
       </c>
       <c r="G84">
         <v>7.58</v>
@@ -8291,28 +8291,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M84">
-        <v>10.7742096</v>
+        <v>10.9056024</v>
       </c>
       <c r="N84">
-        <v>48.99245706666667</v>
+        <v>48.86106426666667</v>
       </c>
       <c r="O84">
-        <v>17.14735997333333</v>
+        <v>17.10137249333333</v>
       </c>
       <c r="P84">
-        <v>31.84509709333333</v>
+        <v>31.75969177333333</v>
       </c>
       <c r="Q84">
-        <v>57.24509709333334</v>
+        <v>57.15969177333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5821357049549716</v>
+        <v>0.6108972104595285</v>
       </c>
       <c r="T84">
-        <v>2.635216934640236</v>
+        <v>2.77653291578999</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.547197324494844</v>
+        <v>5.480363621790087</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1336868757781198</v>
+        <v>0.1331144246643447</v>
       </c>
       <c r="C85">
-        <v>199.605522691341</v>
+        <v>199.7814167734452</v>
       </c>
       <c r="D85">
-        <v>389.233522691341</v>
+        <v>391.7854167734452</v>
       </c>
       <c r="E85">
-        <v>50.90800000000002</v>
+        <v>53.28400000000002</v>
       </c>
       <c r="F85">
-        <v>197.208</v>
+        <v>199.584</v>
       </c>
       <c r="G85">
         <v>7.58</v>
@@ -8373,28 +8373,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M85">
-        <v>10.9056024</v>
+        <v>11.0369952</v>
       </c>
       <c r="N85">
-        <v>48.86106426666667</v>
+        <v>48.72967146666667</v>
       </c>
       <c r="O85">
-        <v>17.10137249333333</v>
+        <v>17.05538501333333</v>
       </c>
       <c r="P85">
-        <v>31.75969177333333</v>
+        <v>31.67428645333333</v>
       </c>
       <c r="Q85">
-        <v>57.15969177333334</v>
+        <v>57.07428645333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6108972104595285</v>
+        <v>0.6432539041521548</v>
       </c>
       <c r="T85">
-        <v>2.77653291578999</v>
+        <v>2.935513394583462</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.480363621790087</v>
+        <v>5.415121197721157</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1331144246643447</v>
+        <v>0.1325419735505697</v>
       </c>
       <c r="C86">
-        <v>199.781416773445</v>
+        <v>199.9909931560486</v>
       </c>
       <c r="D86">
-        <v>391.785416773445</v>
+        <v>394.3709931560486</v>
       </c>
       <c r="E86">
-        <v>53.28399999999999</v>
+        <v>55.66</v>
       </c>
       <c r="F86">
-        <v>199.584</v>
+        <v>201.96</v>
       </c>
       <c r="G86">
         <v>7.58</v>
@@ -8455,28 +8455,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M86">
-        <v>11.0369952</v>
+        <v>11.168388</v>
       </c>
       <c r="N86">
-        <v>48.72967146666667</v>
+        <v>48.59827866666667</v>
       </c>
       <c r="O86">
-        <v>17.05538501333333</v>
+        <v>17.00939753333333</v>
       </c>
       <c r="P86">
-        <v>31.67428645333333</v>
+        <v>31.58888113333333</v>
       </c>
       <c r="Q86">
-        <v>57.07428645333334</v>
+        <v>56.98888113333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6432539041521544</v>
+        <v>0.6799248236704644</v>
       </c>
       <c r="T86">
-        <v>2.93551339458346</v>
+        <v>3.115691270549395</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.415121197721158</v>
+        <v>5.351413889512673</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1325419735505697</v>
+        <v>0.1319695224367946</v>
       </c>
       <c r="C87">
-        <v>199.9909931560486</v>
+        <v>200.2349231253526</v>
       </c>
       <c r="D87">
-        <v>394.3709931560486</v>
+        <v>396.9909231253527</v>
       </c>
       <c r="E87">
-        <v>55.66</v>
+        <v>58.036</v>
       </c>
       <c r="F87">
-        <v>201.96</v>
+        <v>204.336</v>
       </c>
       <c r="G87">
         <v>7.58</v>
@@ -8537,28 +8537,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M87">
-        <v>11.168388</v>
+        <v>11.2997808</v>
       </c>
       <c r="N87">
-        <v>48.59827866666667</v>
+        <v>48.46688586666667</v>
       </c>
       <c r="O87">
-        <v>17.00939753333333</v>
+        <v>16.96341005333333</v>
       </c>
       <c r="P87">
-        <v>31.58888113333333</v>
+        <v>31.50347581333333</v>
       </c>
       <c r="Q87">
-        <v>56.98888113333334</v>
+        <v>56.90347581333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6799248236704644</v>
+        <v>0.721834445977104</v>
       </c>
       <c r="T87">
-        <v>3.115691270549395</v>
+        <v>3.321608843081892</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.351413889512673</v>
+        <v>5.289188146611362</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1319695224367946</v>
+        <v>0.1313970713230195</v>
       </c>
       <c r="C88">
-        <v>200.2349231253526</v>
+        <v>200.5138959251124</v>
       </c>
       <c r="D88">
-        <v>396.9909231253527</v>
+        <v>399.6458959251124</v>
       </c>
       <c r="E88">
-        <v>58.036</v>
+        <v>60.41200000000001</v>
       </c>
       <c r="F88">
-        <v>204.336</v>
+        <v>206.712</v>
       </c>
       <c r="G88">
         <v>7.58</v>
@@ -8619,28 +8619,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M88">
-        <v>11.2997808</v>
+        <v>11.4311736</v>
       </c>
       <c r="N88">
-        <v>48.46688586666667</v>
+        <v>48.33549306666666</v>
       </c>
       <c r="O88">
-        <v>16.96341005333333</v>
+        <v>16.91742257333333</v>
       </c>
       <c r="P88">
-        <v>31.50347581333333</v>
+        <v>31.41807049333333</v>
       </c>
       <c r="Q88">
-        <v>56.90347581333334</v>
+        <v>56.81807049333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.721834445977104</v>
+        <v>0.7701917024847651</v>
       </c>
       <c r="T88">
-        <v>3.321608843081892</v>
+        <v>3.559206042157849</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.289188146611362</v>
+        <v>5.228392880558358</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1313970713230195</v>
+        <v>0.1308246202092444</v>
       </c>
       <c r="C89">
-        <v>200.5138959251124</v>
+        <v>200.8286193611588</v>
       </c>
       <c r="D89">
-        <v>399.6458959251124</v>
+        <v>402.3366193611589</v>
       </c>
       <c r="E89">
-        <v>60.41200000000001</v>
+        <v>62.78800000000001</v>
       </c>
       <c r="F89">
-        <v>206.712</v>
+        <v>209.088</v>
       </c>
       <c r="G89">
         <v>7.58</v>
@@ -8701,28 +8701,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M89">
-        <v>11.4311736</v>
+        <v>11.5625664</v>
       </c>
       <c r="N89">
-        <v>48.33549306666666</v>
+        <v>48.20410026666666</v>
       </c>
       <c r="O89">
-        <v>16.91742257333333</v>
+        <v>16.87143509333333</v>
       </c>
       <c r="P89">
-        <v>31.41807049333333</v>
+        <v>31.33266517333333</v>
       </c>
       <c r="Q89">
-        <v>56.81807049333334</v>
+        <v>56.73266517333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7701917024847651</v>
+        <v>0.8266085017437035</v>
       </c>
       <c r="T89">
-        <v>3.559206042157849</v>
+        <v>3.836402774413135</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.228392880558358</v>
+        <v>5.168979325097467</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1308246202092444</v>
+        <v>0.1302521690954693</v>
       </c>
       <c r="C90">
-        <v>200.8286193611588</v>
+        <v>201.1798204305054</v>
       </c>
       <c r="D90">
-        <v>402.3366193611589</v>
+        <v>405.0638204305055</v>
       </c>
       <c r="E90">
-        <v>62.78800000000001</v>
+        <v>65.16400000000002</v>
       </c>
       <c r="F90">
-        <v>209.088</v>
+        <v>211.464</v>
       </c>
       <c r="G90">
         <v>7.58</v>
@@ -8783,28 +8783,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M90">
-        <v>11.5625664</v>
+        <v>11.6939592</v>
       </c>
       <c r="N90">
-        <v>48.20410026666666</v>
+        <v>48.07270746666666</v>
       </c>
       <c r="O90">
-        <v>16.87143509333333</v>
+        <v>16.82544761333333</v>
       </c>
       <c r="P90">
-        <v>31.33266517333333</v>
+        <v>31.24725985333333</v>
       </c>
       <c r="Q90">
-        <v>56.73266517333333</v>
+        <v>56.64725985333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8266085017437035</v>
+        <v>0.893282900867903</v>
       </c>
       <c r="T90">
-        <v>3.836402774413135</v>
+        <v>4.163998912533016</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.168979325097467</v>
+        <v>5.11090090571435</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1302521690954693</v>
+        <v>0.1296797179816943</v>
       </c>
       <c r="C91">
-        <v>201.1798204305054</v>
+        <v>201.568245976214</v>
       </c>
       <c r="D91">
-        <v>405.0638204305055</v>
+        <v>407.828245976214</v>
       </c>
       <c r="E91">
-        <v>65.16400000000002</v>
+        <v>67.54000000000002</v>
       </c>
       <c r="F91">
-        <v>211.464</v>
+        <v>213.84</v>
       </c>
       <c r="G91">
         <v>7.58</v>
@@ -8865,28 +8865,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M91">
-        <v>11.6939592</v>
+        <v>11.825352</v>
       </c>
       <c r="N91">
-        <v>48.07270746666666</v>
+        <v>47.94131466666666</v>
       </c>
       <c r="O91">
-        <v>16.82544761333333</v>
+        <v>16.77946013333333</v>
       </c>
       <c r="P91">
-        <v>31.24725985333333</v>
+        <v>31.16185453333333</v>
       </c>
       <c r="Q91">
-        <v>56.64725985333334</v>
+        <v>56.56185453333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.893282900867903</v>
+        <v>0.9732921798169426</v>
       </c>
       <c r="T91">
-        <v>4.163998912533016</v>
+        <v>4.557114278276874</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.11090090571435</v>
+        <v>5.054113117873079</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1296797179816943</v>
+        <v>0.1291072668679192</v>
       </c>
       <c r="C92">
-        <v>201.568245976214</v>
+        <v>201.9946633692628</v>
       </c>
       <c r="D92">
-        <v>407.828245976214</v>
+        <v>410.6306633692629</v>
       </c>
       <c r="E92">
-        <v>67.54000000000002</v>
+        <v>69.91600000000003</v>
       </c>
       <c r="F92">
-        <v>213.84</v>
+        <v>216.216</v>
       </c>
       <c r="G92">
         <v>7.58</v>
@@ -8947,28 +8947,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M92">
-        <v>11.825352</v>
+        <v>11.9567448</v>
       </c>
       <c r="N92">
-        <v>47.94131466666666</v>
+        <v>47.80992186666666</v>
       </c>
       <c r="O92">
-        <v>16.77946013333333</v>
+        <v>16.73347265333333</v>
       </c>
       <c r="P92">
-        <v>31.16185453333333</v>
+        <v>31.07644921333333</v>
       </c>
       <c r="Q92">
-        <v>56.56185453333333</v>
+        <v>56.47644921333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9732921798169426</v>
+        <v>1.071081298532436</v>
       </c>
       <c r="T92">
-        <v>4.557114278276874</v>
+        <v>5.037588614186034</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.054113117873079</v>
+        <v>4.998573413281067</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1291072668679192</v>
+        <v>0.1285348157541441</v>
       </c>
       <c r="C93">
-        <v>201.9946633692628</v>
+        <v>202.4598612187203</v>
       </c>
       <c r="D93">
-        <v>410.6306633692629</v>
+        <v>413.4718612187203</v>
       </c>
       <c r="E93">
-        <v>69.91600000000003</v>
+        <v>72.29200000000003</v>
       </c>
       <c r="F93">
-        <v>216.216</v>
+        <v>218.592</v>
       </c>
       <c r="G93">
         <v>7.58</v>
@@ -9029,28 +9029,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M93">
-        <v>11.9567448</v>
+        <v>12.0881376</v>
       </c>
       <c r="N93">
-        <v>47.80992186666666</v>
+        <v>47.67852906666666</v>
       </c>
       <c r="O93">
-        <v>16.73347265333333</v>
+        <v>16.68748517333333</v>
       </c>
       <c r="P93">
-        <v>31.07644921333333</v>
+        <v>30.99104389333333</v>
       </c>
       <c r="Q93">
-        <v>56.47644921333334</v>
+        <v>56.39104389333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.071081298532436</v>
+        <v>1.193317696926802</v>
       </c>
       <c r="T93">
-        <v>5.037588614186034</v>
+        <v>5.638181534072485</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.998573413281067</v>
+        <v>4.94424109357149</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1285348157541441</v>
+        <v>0.127962364640369</v>
       </c>
       <c r="C94">
-        <v>202.4598612187203</v>
+        <v>202.9646501116074</v>
       </c>
       <c r="D94">
-        <v>413.4718612187203</v>
+        <v>416.3526501116075</v>
       </c>
       <c r="E94">
-        <v>72.29200000000003</v>
+        <v>74.66800000000003</v>
       </c>
       <c r="F94">
-        <v>218.592</v>
+        <v>220.968</v>
       </c>
       <c r="G94">
         <v>7.58</v>
@@ -9111,28 +9111,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M94">
-        <v>12.0881376</v>
+        <v>12.2195304</v>
       </c>
       <c r="N94">
-        <v>47.67852906666666</v>
+        <v>47.54713626666666</v>
       </c>
       <c r="O94">
-        <v>16.68748517333333</v>
+        <v>16.64149769333333</v>
       </c>
       <c r="P94">
-        <v>30.99104389333333</v>
+        <v>30.90563857333333</v>
       </c>
       <c r="Q94">
-        <v>56.39104389333333</v>
+        <v>56.30563857333333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.193317696926802</v>
+        <v>1.350478780576701</v>
       </c>
       <c r="T94">
-        <v>5.638181534072485</v>
+        <v>6.410372431069349</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.94424109357149</v>
+        <v>4.891077210844915</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.127962364640369</v>
+        <v>0.127389913526594</v>
       </c>
       <c r="C95">
-        <v>202.9646501116074</v>
+        <v>203.5098633839061</v>
       </c>
       <c r="D95">
-        <v>416.3526501116075</v>
+        <v>419.2738633839061</v>
       </c>
       <c r="E95">
-        <v>74.66800000000003</v>
+        <v>77.04400000000001</v>
       </c>
       <c r="F95">
-        <v>220.968</v>
+        <v>223.344</v>
       </c>
       <c r="G95">
         <v>7.58</v>
@@ -9193,28 +9193,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M95">
-        <v>12.2195304</v>
+        <v>12.3509232</v>
       </c>
       <c r="N95">
-        <v>47.54713626666666</v>
+        <v>47.41574346666666</v>
       </c>
       <c r="O95">
-        <v>16.64149769333333</v>
+        <v>16.59551021333333</v>
       </c>
       <c r="P95">
-        <v>30.90563857333333</v>
+        <v>30.82023325333333</v>
       </c>
       <c r="Q95">
-        <v>56.30563857333333</v>
+        <v>56.22023325333333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.350478780576701</v>
+        <v>1.5600268921099</v>
       </c>
       <c r="T95">
-        <v>6.410372431069349</v>
+        <v>7.439960293731836</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.891077210844915</v>
+        <v>4.839044474559332</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.127389913526594</v>
+        <v>0.1268174624128189</v>
       </c>
       <c r="C96">
-        <v>203.5098633839061</v>
+        <v>204.0963579242551</v>
       </c>
       <c r="D96">
-        <v>419.2738633839061</v>
+        <v>422.2363579242552</v>
       </c>
       <c r="E96">
-        <v>77.04400000000001</v>
+        <v>79.42000000000002</v>
       </c>
       <c r="F96">
-        <v>223.344</v>
+        <v>225.72</v>
       </c>
       <c r="G96">
         <v>7.58</v>
@@ -9275,28 +9275,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M96">
-        <v>12.3509232</v>
+        <v>12.482316</v>
       </c>
       <c r="N96">
-        <v>47.41574346666666</v>
+        <v>47.28435066666666</v>
       </c>
       <c r="O96">
-        <v>16.59551021333333</v>
+        <v>16.54952273333333</v>
       </c>
       <c r="P96">
-        <v>30.82023325333333</v>
+        <v>30.73482793333333</v>
       </c>
       <c r="Q96">
-        <v>56.22023325333333</v>
+        <v>56.13482793333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.5600268921099</v>
+        <v>1.853394248256379</v>
       </c>
       <c r="T96">
-        <v>7.439960293731836</v>
+        <v>8.881383301459319</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.839044474559332</v>
+        <v>4.788107164300811</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1268174624128189</v>
+        <v>0.1262450112990438</v>
       </c>
       <c r="C97">
-        <v>204.0963579242551</v>
+        <v>204.7250150119589</v>
       </c>
       <c r="D97">
-        <v>422.2363579242552</v>
+        <v>425.241015011959</v>
       </c>
       <c r="E97">
-        <v>79.42000000000002</v>
+        <v>81.79600000000002</v>
       </c>
       <c r="F97">
-        <v>225.72</v>
+        <v>228.096</v>
       </c>
       <c r="G97">
         <v>7.58</v>
@@ -9357,28 +9357,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M97">
-        <v>12.482316</v>
+        <v>12.6137088</v>
       </c>
       <c r="N97">
-        <v>47.28435066666666</v>
+        <v>47.15295786666666</v>
       </c>
       <c r="O97">
-        <v>16.54952273333333</v>
+        <v>16.50353525333333</v>
       </c>
       <c r="P97">
-        <v>30.73482793333333</v>
+        <v>30.64942261333333</v>
       </c>
       <c r="Q97">
-        <v>56.13482793333333</v>
+        <v>56.04942261333333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.853394248256379</v>
+        <v>2.293445282476098</v>
       </c>
       <c r="T97">
-        <v>8.881383301459319</v>
+        <v>11.04351781305054</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.788107164300811</v>
+        <v>4.738231048006011</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1262450112990438</v>
+        <v>0.1256725601852687</v>
       </c>
       <c r="C98">
-        <v>204.7250150119589</v>
+        <v>205.3967411910344</v>
       </c>
       <c r="D98">
-        <v>425.241015011959</v>
+        <v>428.2887411910344</v>
       </c>
       <c r="E98">
-        <v>81.79599999999999</v>
+        <v>84.172</v>
       </c>
       <c r="F98">
-        <v>228.096</v>
+        <v>230.472</v>
       </c>
       <c r="G98">
         <v>7.58</v>
@@ -9439,28 +9439,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M98">
-        <v>12.6137088</v>
+        <v>12.7451016</v>
       </c>
       <c r="N98">
-        <v>47.15295786666667</v>
+        <v>47.02156506666667</v>
       </c>
       <c r="O98">
-        <v>16.50353525333333</v>
+        <v>16.45754777333333</v>
       </c>
       <c r="P98">
-        <v>30.64942261333334</v>
+        <v>30.56401729333334</v>
       </c>
       <c r="Q98">
-        <v>56.04942261333333</v>
+        <v>55.96401729333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.293445282476092</v>
+        <v>3.026863672842287</v>
       </c>
       <c r="T98">
-        <v>11.04351781305052</v>
+        <v>14.64707533236921</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.738231048006012</v>
+        <v>4.689383305243064</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1256725601852687</v>
+        <v>0.1251001090714936</v>
       </c>
       <c r="C99">
-        <v>205.3967411910344</v>
+        <v>206.1124691821158</v>
       </c>
       <c r="D99">
-        <v>428.2887411910344</v>
+        <v>431.3804691821158</v>
       </c>
       <c r="E99">
-        <v>84.172</v>
+        <v>86.548</v>
       </c>
       <c r="F99">
-        <v>230.472</v>
+        <v>232.848</v>
       </c>
       <c r="G99">
         <v>7.58</v>
@@ -9521,28 +9521,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M99">
-        <v>12.7451016</v>
+        <v>12.8764944</v>
       </c>
       <c r="N99">
-        <v>47.02156506666667</v>
+        <v>46.89017226666667</v>
       </c>
       <c r="O99">
-        <v>16.45754777333333</v>
+        <v>16.41156029333333</v>
       </c>
       <c r="P99">
-        <v>30.56401729333334</v>
+        <v>30.47861197333333</v>
       </c>
       <c r="Q99">
-        <v>55.96401729333334</v>
+        <v>55.87861197333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.026863672842287</v>
+        <v>4.493700453574676</v>
       </c>
       <c r="T99">
-        <v>14.64707533236921</v>
+        <v>21.85419037100659</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.689383305243064</v>
+        <v>4.641532455189564</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1251001090714936</v>
+        <v>0.1245276579577185</v>
       </c>
       <c r="C100">
-        <v>206.1124691821158</v>
+        <v>206.8731588341404</v>
       </c>
       <c r="D100">
-        <v>431.3804691821158</v>
+        <v>434.5171588341404</v>
       </c>
       <c r="E100">
-        <v>86.548</v>
+        <v>88.92400000000001</v>
       </c>
       <c r="F100">
-        <v>232.848</v>
+        <v>235.224</v>
       </c>
       <c r="G100">
         <v>7.58</v>
@@ -9603,28 +9603,28 @@
         <v>59.76666666666667</v>
       </c>
       <c r="M100">
-        <v>12.8764944</v>
+        <v>13.0078872</v>
       </c>
       <c r="N100">
-        <v>46.89017226666667</v>
+        <v>46.75877946666667</v>
       </c>
       <c r="O100">
-        <v>16.41156029333333</v>
+        <v>16.36557281333333</v>
       </c>
       <c r="P100">
-        <v>30.47861197333333</v>
+        <v>30.39320665333333</v>
       </c>
       <c r="Q100">
-        <v>55.87861197333334</v>
+        <v>55.79320665333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.493700453574676</v>
+        <v>8.894210795771846</v>
       </c>
       <c r="T100">
-        <v>21.85419037100659</v>
+        <v>43.47553548691875</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.641532455189564</v>
+        <v>4.594648288975527</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1245276579577185</v>
-      </c>
-      <c r="C101">
-        <v>206.8731588341404</v>
-      </c>
-      <c r="D101">
-        <v>434.5171588341404</v>
-      </c>
-      <c r="E101">
-        <v>88.92400000000001</v>
-      </c>
-      <c r="F101">
-        <v>235.224</v>
-      </c>
-      <c r="G101">
-        <v>7.58</v>
-      </c>
-      <c r="H101">
-        <v>91.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>85.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>25.4</v>
-      </c>
-      <c r="L101">
-        <v>59.76666666666667</v>
-      </c>
-      <c r="M101">
-        <v>13.0078872</v>
-      </c>
-      <c r="N101">
-        <v>46.75877946666667</v>
-      </c>
-      <c r="O101">
-        <v>16.36557281333333</v>
-      </c>
-      <c r="P101">
-        <v>30.39320665333333</v>
-      </c>
-      <c r="Q101">
-        <v>55.79320665333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.894210795771846</v>
-      </c>
-      <c r="T101">
-        <v>43.47553548691875</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.594648288975527</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
